--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -5104,6 +5104,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -5322,15 +5331,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5340,6 +5340,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5354,14 +5362,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C61B4AE-75EF-4B30-AAC2-480FB04DC4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359C347D-94BD-4E0A-B664-1C3B3E3C7055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="318">
   <si>
     <t>武器</t>
   </si>
@@ -1005,6 +1005,12 @@
   </si>
   <si>
     <t>使用这种武器攻击会使目标的治疗降为0.持续10秒</t>
+  </si>
+  <si>
+    <t>百病之斧</t>
+  </si>
+  <si>
+    <t>下雨时造成双倍伤害</t>
   </si>
 </sst>
 </file>
@@ -2010,7 +2016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396CB4A7-922E-403D-B02B-B84252EDCF5F}">
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.796875" customWidth="1"/>
@@ -3719,62 +3725,64 @@
         <v>170</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A77" s="28" t="s">
-        <v>171</v>
+        <v>316</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C77" s="7" t="s">
-        <v>168</v>
+      <c r="C77" s="14" t="s">
+        <v>289</v>
       </c>
       <c r="D77" s="6">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="E77" s="6">
         <v>1.6</v>
       </c>
       <c r="F77" s="6">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="24" t="s">
-        <v>172</v>
+        <v>317</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C78" s="8" t="s">
-        <v>174</v>
+      <c r="C78" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="D78" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="E78" s="6">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F78" s="6">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="27" x14ac:dyDescent="0.35">
-      <c r="A79" s="21" t="s">
-        <v>176</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="28" t="s">
+        <v>173</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C79" s="10"/>
+        <v>163</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>174</v>
+      </c>
       <c r="D79" s="6">
         <v>1.1000000000000001</v>
       </c>
@@ -3784,60 +3792,58 @@
       <c r="F79" s="6">
         <v>59</v>
       </c>
-      <c r="G79" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="H79" s="41"/>
-    </row>
-    <row r="80" spans="1:8" ht="28.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="B80" s="6">
-        <v>62</v>
+      <c r="G79" s="2"/>
+      <c r="H79" s="24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="27" x14ac:dyDescent="0.35">
+      <c r="A80" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="6">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E80" s="6">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="F80" s="6">
-        <v>67</v>
-      </c>
-      <c r="G80" s="2"/>
-      <c r="H80" s="39" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>182</v>
+        <v>59</v>
+      </c>
+      <c r="G80" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="H80" s="41"/>
+    </row>
+    <row r="81" spans="1:8" ht="28.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B81" s="6">
+        <v>62</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="6">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="E81" s="6">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="F81" s="6">
-        <v>56</v>
-      </c>
-      <c r="G81" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="H81" s="40" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="27.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="21" t="s">
-        <v>184</v>
+        <v>67</v>
+      </c>
+      <c r="G81" s="2"/>
+      <c r="H81" s="39" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>182</v>
@@ -3859,73 +3865,77 @@
         <v>183</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="27.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="6">
         <v>0.9</v>
       </c>
       <c r="E83" s="6">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="F83" s="6">
         <v>56</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="H83" s="22"/>
-    </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="29" t="s">
-        <v>188</v>
+        <v>156</v>
+      </c>
+      <c r="H83" s="40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="21" t="s">
+        <v>185</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="6">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E84" s="6">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6">
-        <v>67</v>
-      </c>
-      <c r="G84" s="2"/>
-      <c r="H84" s="39" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="B85" s="6">
-        <v>65</v>
+        <v>56</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="H84" s="22"/>
+    </row>
+    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="6">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E85" s="6">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="F85" s="6">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G85" s="2"/>
-      <c r="H85" s="22"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H85" s="39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B86" s="6">
         <v>65</v>
@@ -3938,38 +3948,34 @@
         <v>7</v>
       </c>
       <c r="F86" s="6">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="22"/>
     </row>
-    <row r="87" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A87" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>194</v>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" s="6">
+        <v>65</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="6">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E87" s="6">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="F87" s="6">
-        <v>59</v>
-      </c>
-      <c r="G87" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="H87" s="40" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="25" t="s">
-        <v>196</v>
+        <v>84</v>
+      </c>
+      <c r="G87" s="2"/>
+      <c r="H87" s="22"/>
+    </row>
+    <row r="88" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A88" s="30" t="s">
+        <v>193</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>194</v>
@@ -3982,34 +3988,38 @@
         <v>1.7</v>
       </c>
       <c r="F88" s="6">
-        <v>84</v>
-      </c>
-      <c r="G88" s="2"/>
-      <c r="H88" s="22"/>
-    </row>
-    <row r="89" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A89" s="21" t="s">
-        <v>197</v>
+        <v>59</v>
+      </c>
+      <c r="G88" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="H88" s="40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="25" t="s">
+        <v>196</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="E89" s="6">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F89" s="6">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="22"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="25" t="s">
-        <v>199</v>
+    <row r="90" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
+      <c r="A90" s="21" t="s">
+        <v>197</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>198</v>
@@ -4022,148 +4032,148 @@
         <v>1.8</v>
       </c>
       <c r="F90" s="6">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="22"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="29" t="s">
-        <v>200</v>
+      <c r="A91" s="25" t="s">
+        <v>199</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="10"/>
+      <c r="D91" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E91" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="F91" s="6">
+        <v>91</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="22"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D92" s="6">
         <v>0.9</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E92" s="6">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F92" s="6">
         <v>46</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="42" t="s">
+      <c r="G92" s="2"/>
+      <c r="H92" s="42" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A92" s="29" t="s">
+    <row r="93" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A93" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="B92" s="6">
+      <c r="B93" s="6">
         <v>70</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C93" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D92" s="6">
+      <c r="D93" s="6">
         <v>0.8</v>
       </c>
-      <c r="E92" s="6">
+      <c r="E93" s="6">
         <v>1.5</v>
-      </c>
-      <c r="F92" s="6">
-        <v>72</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="43" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="B93" s="6">
-        <v>77</v>
-      </c>
-      <c r="C93" s="10"/>
-      <c r="D93" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="E93" s="6">
-        <v>1.4</v>
       </c>
       <c r="F93" s="6">
         <v>72</v>
       </c>
       <c r="G93" s="2"/>
-      <c r="H93" s="24" t="s">
-        <v>207</v>
+      <c r="H93" s="43" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="28" t="s">
-        <v>125</v>
+      <c r="A94" s="29" t="s">
+        <v>206</v>
       </c>
       <c r="B94" s="6">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="6">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="E94" s="6">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F94" s="6">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="G94" s="2"/>
-      <c r="H94" s="40" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="29" t="s">
-        <v>208</v>
+      <c r="H94" s="24" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="B95" s="6">
         <v>80</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="6">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="E95" s="6">
-        <v>2.2999999999999998</v>
+        <v>1.3</v>
       </c>
       <c r="F95" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="39" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A96" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>211</v>
+      <c r="H95" s="40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" s="6">
+        <v>80</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="6">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E96" s="6">
         <v>2.2999999999999998</v>
       </c>
       <c r="F96" s="6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="22"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="25" t="s">
-        <v>212</v>
+      <c r="H96" s="39" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
+      <c r="A97" s="21" t="s">
+        <v>210</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>211</v>
@@ -4176,21 +4186,19 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F97" s="6">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="22"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="29" t="s">
-        <v>213</v>
+      <c r="A98" s="25" t="s">
+        <v>212</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C98" s="7" t="s">
-        <v>214</v>
-      </c>
+      <c r="C98" s="10"/>
       <c r="D98" s="6">
         <v>0.9</v>
       </c>
@@ -4198,22 +4206,20 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F98" s="6">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="G98" s="2"/>
-      <c r="H98" s="24" t="s">
-        <v>215</v>
-      </c>
+      <c r="H98" s="22"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C99" s="8" t="s">
-        <v>217</v>
+      <c r="C99" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="D99" s="6">
         <v>0.9</v>
@@ -4224,142 +4230,144 @@
       <c r="F99" s="6">
         <v>46</v>
       </c>
-      <c r="G99" s="3"/>
-      <c r="H99" s="24"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="24" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D100" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="E100" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F100" s="6">
+        <v>46</v>
+      </c>
+      <c r="G100" s="3"/>
+      <c r="H100" s="24"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="B100" s="6">
+      <c r="B101" s="6">
         <v>83</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E100" s="6">
-        <v>1.6</v>
-      </c>
-      <c r="F100" s="6">
-        <v>72</v>
-      </c>
-      <c r="G100" s="2"/>
-      <c r="H100" s="24" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="6">
-        <v>0.9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E101" s="6">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F101" s="6">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="24" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="44" t="s">
-        <v>223</v>
+      <c r="A102" s="28" t="s">
+        <v>220</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C102" s="10"/>
       <c r="D102" s="6">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E102" s="6">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="F102" s="6">
         <v>56</v>
       </c>
       <c r="G102" s="2"/>
-      <c r="H102" s="22"/>
-    </row>
-    <row r="103" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B103" s="6">
-        <v>90</v>
+      <c r="H102" s="24" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="6">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E103" s="6">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6">
-        <v>29</v>
-      </c>
-      <c r="G103" s="12" t="s">
-        <v>226</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="G103" s="2"/>
       <c r="H103" s="22"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="28" t="s">
-        <v>227</v>
+    <row r="104" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="25" t="s">
+        <v>225</v>
       </c>
       <c r="B104" s="6">
         <v>90</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="6">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E104" s="6">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="F104" s="6">
-        <v>50</v>
-      </c>
-      <c r="G104" s="2"/>
-      <c r="H104" s="24" t="s">
-        <v>228</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G104" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="H104" s="22"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="29" t="s">
-        <v>305</v>
+      <c r="A105" s="28" t="s">
+        <v>227</v>
       </c>
       <c r="B105" s="6">
         <v>90</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="6">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="E105" s="6">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="F105" s="6">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="24" t="s">
-        <v>306</v>
+        <v>228</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="29" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B106" s="6">
         <v>90</v>
@@ -4372,7 +4380,7 @@
         <v>6</v>
       </c>
       <c r="F106" s="6">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="24" t="s">
@@ -4381,141 +4389,141 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="29" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="B107" s="6">
         <v>90</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="6">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="E107" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F107" s="6">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="24" t="s">
-        <v>135</v>
+        <v>306</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
+      </c>
+      <c r="B108" s="6">
+        <v>90</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="6">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="E108" s="6">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="F108" s="6">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C109" s="10"/>
+      <c r="D109" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="E109" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="F109" s="6">
+        <v>77</v>
+      </c>
+      <c r="G109" s="2"/>
+      <c r="H109" s="24" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="45" t="s">
+    <row r="110" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="45" t="s">
         <v>288</v>
-      </c>
-      <c r="B109" s="6">
-        <v>95</v>
-      </c>
-      <c r="C109" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="D109" s="6">
-        <v>1</v>
-      </c>
-      <c r="E109" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="F109" s="6">
-        <v>46</v>
-      </c>
-      <c r="G109" s="2"/>
-      <c r="H109" s="46" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="29" t="s">
-        <v>233</v>
       </c>
       <c r="B110" s="6">
         <v>95</v>
       </c>
-      <c r="C110" s="10"/>
+      <c r="C110" s="14" t="s">
+        <v>289</v>
+      </c>
       <c r="D110" s="6">
         <v>1</v>
       </c>
       <c r="E110" s="6">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F110" s="6">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G110" s="2"/>
-      <c r="H110" s="39" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H110" s="46" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="29" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B111" s="6">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="6">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E111" s="6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="39" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="29" t="s">
-        <v>307</v>
+        <v>235</v>
       </c>
       <c r="B112" s="6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="6">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E112" s="6">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="F112" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="39" t="s">
-        <v>308</v>
+        <v>236</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="29" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B113" s="6">
         <v>100</v>
@@ -4528,7 +4536,7 @@
         <v>2.1</v>
       </c>
       <c r="F113" s="6">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="39" t="s">
@@ -4537,58 +4545,56 @@
     </row>
     <row r="114" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="29" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B114" s="6">
         <v>100</v>
       </c>
       <c r="C114" s="10"/>
       <c r="D114" s="6">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E114" s="6">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="F114" s="6">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="G114" s="2"/>
-      <c r="H114" s="46" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H114" s="39" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="29" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="B115" s="6">
         <v>100</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="6">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E115" s="6">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="F115" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G115" s="2"/>
-      <c r="H115" s="39" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="H115" s="46" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C116" s="9" t="s">
-        <v>241</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="B116" s="6">
+        <v>100</v>
+      </c>
+      <c r="C116" s="10"/>
       <c r="D116" s="6">
         <v>0.8</v>
       </c>
@@ -4596,60 +4602,62 @@
         <v>2</v>
       </c>
       <c r="F116" s="6">
+        <v>50</v>
+      </c>
+      <c r="G116" s="2"/>
+      <c r="H116" s="39" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A117" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D117" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E117" s="6">
+        <v>2</v>
+      </c>
+      <c r="F117" s="6">
         <v>46</v>
-      </c>
-      <c r="G116" s="2"/>
-      <c r="H116" s="24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="B117" s="6">
-        <v>100</v>
-      </c>
-      <c r="C117" s="10"/>
-      <c r="D117" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="E117" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="F117" s="6">
-        <v>59</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>240</v>
+        <v>243</v>
+      </c>
+      <c r="B118" s="6">
+        <v>100</v>
       </c>
       <c r="C118" s="10"/>
       <c r="D118" s="6">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="E118" s="6">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F118" s="6">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G118" s="2"/>
-      <c r="H118" s="34" t="s">
-        <v>246</v>
+      <c r="H118" s="24" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="29" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>240</v>
@@ -4659,155 +4667,155 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="E119" s="6">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F119" s="6">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G119" s="2"/>
-      <c r="H119" s="24" t="s">
-        <v>248</v>
+      <c r="H119" s="34" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="B120" s="6">
-        <v>100</v>
+        <v>247</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="C120" s="10"/>
       <c r="D120" s="6">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E120" s="6">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F120" s="6">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="24" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="B121" s="6">
+        <v>100</v>
+      </c>
+      <c r="C121" s="10"/>
+      <c r="D121" s="6">
+        <v>1.3</v>
+      </c>
+      <c r="E121" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="F121" s="6">
+        <v>72</v>
+      </c>
+      <c r="G121" s="2"/>
+      <c r="H121" s="24" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="29" t="s">
+    <row r="122" spans="1:8" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="29" t="s">
         <v>251</v>
-      </c>
-      <c r="B121" s="6">
-        <v>105</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="D121" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="E121" s="6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F121" s="6">
-        <v>46</v>
-      </c>
-      <c r="G121" s="2"/>
-      <c r="H121" s="39" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="29" t="s">
-        <v>254</v>
       </c>
       <c r="B122" s="6">
         <v>105</v>
       </c>
-      <c r="C122" s="8" t="s">
-        <v>217</v>
+      <c r="C122" s="7" t="s">
+        <v>252</v>
       </c>
       <c r="D122" s="6">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E122" s="6">
-        <v>1.9</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F122" s="6">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="39" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="28" t="s">
-        <v>256</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="29" t="s">
+        <v>254</v>
       </c>
       <c r="B123" s="6">
-        <v>107</v>
-      </c>
-      <c r="C123" s="10"/>
+        <v>105</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>217</v>
+      </c>
       <c r="D123" s="6">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E123" s="6">
         <v>1.9</v>
       </c>
       <c r="F123" s="6">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="G123" s="2"/>
-      <c r="H123" s="34" t="s">
-        <v>257</v>
+      <c r="H123" s="39" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="29" t="s">
-        <v>258</v>
+      <c r="A124" s="28" t="s">
+        <v>256</v>
       </c>
       <c r="B124" s="6">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C124" s="10"/>
       <c r="D124" s="6">
         <v>0.9</v>
       </c>
       <c r="E124" s="6">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F124" s="6">
         <v>67</v>
       </c>
       <c r="G124" s="2"/>
-      <c r="H124" s="24" t="s">
-        <v>259</v>
+      <c r="H124" s="34" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="29" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B125" s="6">
         <v>110</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="6">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E125" s="6">
-        <v>2.2999999999999998</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6">
         <v>67</v>
       </c>
       <c r="G125" s="2"/>
-      <c r="H125" s="34" t="s">
-        <v>261</v>
+      <c r="H125" s="24" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="29" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B126" s="6">
         <v>110</v>
@@ -4820,7 +4828,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F126" s="6">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="34" t="s">
@@ -4829,172 +4837,172 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="29" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B127" s="6">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="6">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E127" s="6">
-        <v>1.5</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F127" s="6">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="G127" s="2"/>
-      <c r="H127" s="24" t="s">
-        <v>264</v>
+      <c r="H127" s="34" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="29" t="s">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="B128" s="6">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C128" s="10"/>
       <c r="D128" s="6">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E128" s="6">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="F128" s="6">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="24" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="28" t="s">
-        <v>282</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>284</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B129" s="6">
+        <v>120</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="6">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E129" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F129" s="6">
-        <v>50</v>
-      </c>
-      <c r="G129" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="H129" s="39" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="B130" s="6">
-        <v>128</v>
+        <v>100</v>
+      </c>
+      <c r="G129" s="2"/>
+      <c r="H129" s="24" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>284</v>
       </c>
       <c r="C130" s="10"/>
       <c r="D130" s="6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E130" s="6">
         <v>2</v>
       </c>
       <c r="F130" s="6">
-        <v>46</v>
-      </c>
-      <c r="G130" s="2"/>
-      <c r="H130" s="24" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>217</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G130" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="H130" s="39" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="B131" s="6">
+        <v>128</v>
+      </c>
+      <c r="C131" s="10"/>
       <c r="D131" s="6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E131" s="6">
         <v>2</v>
       </c>
       <c r="F131" s="6">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G131" s="2"/>
-      <c r="H131" s="40" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="29" t="s">
-        <v>280</v>
+      <c r="H131" s="24" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="47" t="s">
+        <v>267</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="C132" s="10"/>
+      <c r="C132" s="8" t="s">
+        <v>217</v>
+      </c>
       <c r="D132" s="6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E132" s="6">
         <v>2</v>
       </c>
       <c r="F132" s="6">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="40" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="B133" s="6">
-        <v>130</v>
+        <v>280</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>268</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E133" s="6">
-        <v>2.2999999999999998</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G133" s="2"/>
-      <c r="H133" s="34" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H133" s="40" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="29" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B134" s="6">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C134" s="10"/>
       <c r="D134" s="6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E134" s="6">
         <v>2.2999999999999998</v>
@@ -5003,13 +5011,13 @@
         <v>50</v>
       </c>
       <c r="G134" s="2"/>
-      <c r="H134" s="39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H134" s="34" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="29" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B135" s="6">
         <v>132</v>
@@ -5022,16 +5030,16 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F135" s="6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="39" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="29" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B136" s="6">
         <v>132</v>
@@ -5044,54 +5052,76 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F136" s="6">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="39" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" s="54" t="s">
+    <row r="137" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="B137" s="6">
+        <v>132</v>
+      </c>
+      <c r="C137" s="10"/>
+      <c r="D137" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E137" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F137" s="6">
+        <v>63</v>
+      </c>
+      <c r="G137" s="2"/>
+      <c r="H137" s="39" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="54" t="s">
         <v>277</v>
       </c>
-      <c r="B137" s="55" t="s">
+      <c r="B138" s="55" t="s">
         <v>278</v>
       </c>
-      <c r="C137" s="56"/>
-      <c r="D137" s="55">
+      <c r="C138" s="56"/>
+      <c r="D138" s="55">
         <v>0.8</v>
       </c>
-      <c r="E137" s="55">
+      <c r="E138" s="55">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F137" s="55">
+      <c r="F138" s="55">
         <v>50</v>
       </c>
-      <c r="G137" s="57"/>
-      <c r="H137" s="58" t="s">
+      <c r="G138" s="57"/>
+      <c r="H138" s="58" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A138" s="50" t="s">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="50" t="s">
         <v>313</v>
       </c>
-      <c r="B138" s="15" t="s">
+      <c r="B139" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="C138" s="51"/>
-      <c r="D138" s="15">
+      <c r="C139" s="51"/>
+      <c r="D139" s="15">
         <v>1</v>
       </c>
-      <c r="E138" s="15">
+      <c r="E139" s="15">
         <v>2</v>
       </c>
-      <c r="F138" s="15" t="s">
+      <c r="F139" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="G138" s="52"/>
-      <c r="H138" s="53" t="s">
+      <c r="G139" s="52"/>
+      <c r="H139" s="53" t="s">
         <v>315</v>
       </c>
     </row>
@@ -5104,12 +5134,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5332,17 +5361,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5367,18 +5406,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359C347D-94BD-4E0A-B664-1C3B3E3C7055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A246D1F-50B5-458B-BD3F-1412C756A57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="317">
   <si>
     <t>武器</t>
   </si>
@@ -963,9 +963,6 @@
   </si>
   <si>
     <t>无视护甲目标对远程武器所具有的额外防御</t>
-  </si>
-  <si>
-    <t>待测</t>
   </si>
   <si>
     <t>铁斧</t>
@@ -1037,6 +1034,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1044,6 +1042,7 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2341,7 +2340,7 @@
     </row>
     <row r="15" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A15" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B15" s="1">
         <v>18</v>
@@ -2358,7 +2357,7 @@
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="49" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
@@ -2539,7 +2538,7 @@
     </row>
     <row r="24" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A24" s="27" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B24" s="1">
         <v>20</v>
@@ -2556,7 +2555,7 @@
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="49" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
@@ -3727,7 +3726,7 @@
     </row>
     <row r="77" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A77" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>163</v>
@@ -3746,7 +3745,7 @@
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="24" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
@@ -4367,7 +4366,7 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="29" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B106" s="6">
         <v>90</v>
@@ -4384,12 +4383,12 @@
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B107" s="6">
         <v>90</v>
@@ -4406,7 +4405,7 @@
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
@@ -4523,7 +4522,7 @@
     </row>
     <row r="113" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="29" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B113" s="6">
         <v>100</v>
@@ -4540,12 +4539,12 @@
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="29" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B114" s="6">
         <v>100</v>
@@ -4562,7 +4561,7 @@
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5105,10 +5104,10 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="50" t="s">
+        <v>312</v>
+      </c>
+      <c r="B139" s="15" t="s">
         <v>313</v>
-      </c>
-      <c r="B139" s="15" t="s">
-        <v>314</v>
       </c>
       <c r="C139" s="51"/>
       <c r="D139" s="15">
@@ -5117,12 +5116,12 @@
       <c r="E139" s="15">
         <v>2</v>
       </c>
-      <c r="F139" s="15" t="s">
-        <v>302</v>
+      <c r="F139" s="15">
+        <v>143</v>
       </c>
       <c r="G139" s="52"/>
       <c r="H139" s="53" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -5134,14 +5133,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -5360,6 +5351,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5370,23 +5369,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5405,6 +5387,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
   <ds:schemaRefs>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A246D1F-50B5-458B-BD3F-1412C756A57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E438CC-48B2-435E-8457-5625531D6BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="320">
   <si>
     <t>武器</t>
   </si>
@@ -1008,6 +1008,15 @@
   </si>
   <si>
     <t>下雨时造成双倍伤害</t>
+  </si>
+  <si>
+    <t>铁锭*2 桦木板*2</t>
+  </si>
+  <si>
+    <t>变种剑高级图纸；磨1比骑士剑伤害高1</t>
+  </si>
+  <si>
+    <t>优质弓弦*4；铁锭*8；桦木板*10；皮条*12</t>
   </si>
 </sst>
 </file>
@@ -1496,7 +1505,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1672,6 +1681,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2355,7 +2367,9 @@
       <c r="F15" s="6">
         <v>84</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="2" t="s">
+        <v>317</v>
+      </c>
       <c r="H15" s="49" t="s">
         <v>309</v>
       </c>
@@ -2553,7 +2567,9 @@
       <c r="F24" s="16">
         <v>84</v>
       </c>
-      <c r="G24" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>317</v>
+      </c>
       <c r="H24" s="49" t="s">
         <v>308</v>
       </c>
@@ -3885,7 +3901,7 @@
         <v>156</v>
       </c>
       <c r="H83" s="40" t="s">
-        <v>183</v>
+        <v>318</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3949,7 +3965,9 @@
       <c r="F86" s="6">
         <v>59</v>
       </c>
-      <c r="G86" s="2"/>
+      <c r="G86" s="60" t="s">
+        <v>319</v>
+      </c>
       <c r="H86" s="22"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
@@ -5133,6 +5151,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -5351,14 +5377,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5369,6 +5387,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5387,23 +5422,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
   <ds:schemaRefs>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E438CC-48B2-435E-8457-5625531D6BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEF720C-1D5A-4B9A-A4C0-81FB643F56DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -1016,7 +1016,7 @@
     <t>变种剑高级图纸；磨1比骑士剑伤害高1</t>
   </si>
   <si>
-    <t>优质弓弦*4；铁锭*8；桦木板*10；皮条*12</t>
+    <t>优质弓弦*4 铁锭*8 桦木板*10 皮条*12</t>
   </si>
 </sst>
 </file>
@@ -1679,11 +1679,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2038,16 +2038,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.4" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="60" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
@@ -3965,7 +3965,7 @@
       <c r="F86" s="6">
         <v>59</v>
       </c>
-      <c r="G86" s="60" t="s">
+      <c r="G86" s="59" t="s">
         <v>319</v>
       </c>
       <c r="H86" s="22"/>
@@ -5151,11 +5151,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5378,27 +5379,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5423,9 +5414,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEF720C-1D5A-4B9A-A4C0-81FB643F56DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718C23A5-8CB9-42F9-872B-D09AF11BB725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -80,9 +80,6 @@
     <t>400秒</t>
   </si>
   <si>
-    <t>原松木*1 绳子*1 亚麻纤维*1</t>
-  </si>
-  <si>
     <t>每次攻击耗费5秒；可吓退夜游神</t>
   </si>
   <si>
@@ -201,9 +198,6 @@
   </si>
   <si>
     <t>锹</t>
-  </si>
-  <si>
-    <t>松木板*1 铜锭*1 青铜钉*1</t>
   </si>
   <si>
     <t>匕首</t>
@@ -1017,6 +1011,12 @@
   </si>
   <si>
     <t>优质弓弦*4 铁锭*8 桦木板*10 皮条*12</t>
+  </si>
+  <si>
+    <t>松木板*5 铜锭*3 青铜钉*2</t>
+  </si>
+  <si>
+    <t>原松木*2 绳子*2 亚麻纤维*3</t>
   </si>
 </sst>
 </file>
@@ -2039,7 +2039,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21.4" thickBot="1" x14ac:dyDescent="0.7">
       <c r="A1" s="60" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B1" s="60"/>
       <c r="C1" s="60"/>
@@ -2113,15 +2113,15 @@
         <v>13</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H4" s="24" t="s">
         <v>14</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1">
         <v>8</v>
@@ -2137,15 +2137,15 @@
         <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="24" t="s">
         <v>17</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1">
         <v>8</v>
@@ -2161,15 +2161,15 @@
         <v>50</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1">
         <v>9</v>
@@ -2185,15 +2185,15 @@
         <v>50</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1">
         <v>9</v>
@@ -2209,15 +2209,15 @@
         <v>50</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1">
         <v>12</v>
@@ -2233,18 +2233,18 @@
         <v>67</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="24" t="s">
         <v>26</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="6">
@@ -2261,7 +2261,7 @@
     </row>
     <row r="11" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1">
         <v>13</v>
@@ -2277,18 +2277,18 @@
         <v>67</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="6">
@@ -2301,17 +2301,17 @@
         <v>56</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H12" s="24"/>
       <c r="L12" s="48"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="6">
@@ -2324,18 +2324,18 @@
         <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="6">
@@ -2352,7 +2352,7 @@
     </row>
     <row r="15" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A15" s="27" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B15" s="1">
         <v>18</v>
@@ -2368,18 +2368,18 @@
         <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H15" s="49" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="6">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="6">
@@ -2416,13 +2416,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="D18" s="6">
         <v>1.4</v>
@@ -2435,18 +2435,18 @@
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="D19" s="6">
         <v>0.8</v>
@@ -2459,18 +2459,18 @@
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A20" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="D20" s="3">
         <v>1.4</v>
@@ -2483,15 +2483,15 @@
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="6">
@@ -2504,16 +2504,16 @@
         <v>84</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>55</v>
+        <v>318</v>
       </c>
       <c r="H21" s="22"/>
     </row>
     <row r="22" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="6">
@@ -2526,16 +2526,16 @@
         <v>100</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H22" s="22"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="6">
@@ -2552,7 +2552,7 @@
     </row>
     <row r="24" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A24" s="27" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B24" s="1">
         <v>20</v>
@@ -2568,18 +2568,18 @@
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H24" s="49" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="3">
@@ -2592,18 +2592,18 @@
         <v>84</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>55</v>
+        <v>318</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="3">
@@ -2617,15 +2617,15 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="6">
@@ -2638,18 +2638,18 @@
         <v>100</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="6">
@@ -2662,18 +2662,18 @@
         <v>100</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A29" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="6">
@@ -2686,16 +2686,16 @@
         <v>42</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H29" s="22"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="6">
@@ -2709,15 +2709,15 @@
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="6">
@@ -2734,10 +2734,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="6">
@@ -2754,7 +2754,7 @@
     </row>
     <row r="33" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A33" s="31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B33" s="6">
         <v>26</v>
@@ -2770,16 +2770,16 @@
         <v>63</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H33" s="22"/>
     </row>
     <row r="34" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="6">
@@ -2792,16 +2792,16 @@
         <v>91</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H34" s="22"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="6">
@@ -2818,10 +2818,10 @@
     </row>
     <row r="36" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="6">
@@ -2834,18 +2834,18 @@
         <v>42</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A37" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="6">
@@ -2858,15 +2858,15 @@
         <v>42</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A38" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B38" s="6">
         <v>27</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="39" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A39" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="6">
@@ -2902,18 +2902,18 @@
         <v>91</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="6">
@@ -2926,21 +2926,21 @@
         <v>250</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B41" s="6">
         <v>30</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D41" s="6">
         <v>0.8</v>
@@ -2953,18 +2953,18 @@
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A42" s="32" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B42" s="6">
         <v>30</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D42" s="6">
         <v>0.8</v>
@@ -2977,18 +2977,18 @@
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B43" s="6">
         <v>30</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D43" s="6">
         <v>0.8</v>
@@ -3001,15 +3001,15 @@
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A44" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="6">
@@ -3022,16 +3022,16 @@
         <v>67</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H44" s="22"/>
     </row>
     <row r="45" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A45" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="6">
@@ -3044,18 +3044,18 @@
         <v>67</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A46" s="21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="6">
@@ -3068,13 +3068,13 @@
         <v>77</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H46" s="22"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B47" s="6">
         <v>35</v>
@@ -3094,10 +3094,10 @@
     </row>
     <row r="48" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A48" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="6">
@@ -3110,16 +3110,16 @@
         <v>84</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H48" s="22"/>
     </row>
     <row r="49" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A49" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="6">
@@ -3132,16 +3132,16 @@
         <v>91</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H49" s="22"/>
     </row>
     <row r="50" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A50" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="6">
@@ -3154,18 +3154,18 @@
         <v>77</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A51" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="6">
@@ -3178,18 +3178,18 @@
         <v>77</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A52" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="6">
@@ -3202,18 +3202,18 @@
         <v>84</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A53" s="21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="6">
@@ -3226,18 +3226,18 @@
         <v>91</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A54" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="6">
@@ -3250,15 +3250,15 @@
         <v>91</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B55" s="6">
         <v>42</v>
@@ -3278,10 +3278,10 @@
     </row>
     <row r="56" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A56" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="6">
@@ -3294,16 +3294,16 @@
         <v>72</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H56" s="22"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="6">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A58" s="21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B58" s="6">
         <v>45</v>
@@ -3336,16 +3336,16 @@
         <v>35</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H58" s="22"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="28" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="6">
@@ -3359,15 +3359,15 @@
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="34" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="6">
@@ -3381,18 +3381,18 @@
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="34" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A61" s="29" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D61" s="6">
         <v>1.5</v>
@@ -3405,18 +3405,18 @@
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="24" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A62" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B62" s="6">
         <v>50</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D62" s="6">
         <v>1</v>
@@ -3429,12 +3429,12 @@
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="A63" s="28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B63" s="6">
         <v>52</v>
@@ -3451,12 +3451,12 @@
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="36" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B64" s="6">
         <v>55</v>
@@ -3472,13 +3472,13 @@
         <v>35</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H64" s="37"/>
     </row>
     <row r="65" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B65" s="6">
         <v>55</v>
@@ -3495,18 +3495,18 @@
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="28" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B66" s="6">
         <v>55</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D66" s="6">
         <v>1</v>
@@ -3519,15 +3519,15 @@
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="6">
@@ -3541,15 +3541,15 @@
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="6">
@@ -3563,15 +3563,15 @@
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="24" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="A69" s="38" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="6">
@@ -3584,16 +3584,16 @@
         <v>56</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H69" s="22"/>
     </row>
     <row r="70" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="6">
@@ -3610,10 +3610,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="25" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="6">
@@ -3630,7 +3630,7 @@
     </row>
     <row r="72" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="29" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B72" s="6">
         <v>60</v>
@@ -3647,15 +3647,15 @@
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="39" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="28" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="6">
@@ -3672,10 +3672,10 @@
     </row>
     <row r="74" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A74" s="29" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="6">
@@ -3689,18 +3689,18 @@
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="39" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="44.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B75" s="6">
         <v>60</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D75" s="6">
         <v>1</v>
@@ -3713,18 +3713,18 @@
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="40" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="28" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B76" s="6">
         <v>60</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D76" s="6">
         <v>0.9</v>
@@ -3737,18 +3737,18 @@
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A77" s="28" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D77" s="6">
         <v>0.9</v>
@@ -3761,18 +3761,18 @@
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="24" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="28" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D78" s="6">
         <v>1.1000000000000001</v>
@@ -3785,18 +3785,18 @@
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D79" s="6">
         <v>1.1000000000000001</v>
@@ -3809,15 +3809,15 @@
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="27" x14ac:dyDescent="0.35">
       <c r="A80" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="6">
@@ -3830,13 +3830,13 @@
         <v>59</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H80" s="41"/>
     </row>
     <row r="81" spans="1:8" ht="28.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="28" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B81" s="6">
         <v>62</v>
@@ -3853,15 +3853,15 @@
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="39" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="6">
@@ -3874,18 +3874,18 @@
         <v>56</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H82" s="40" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="27.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="6">
@@ -3898,18 +3898,18 @@
         <v>56</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H83" s="40" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="6">
@@ -3922,16 +3922,16 @@
         <v>56</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H84" s="22"/>
     </row>
     <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="6">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="25" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B86" s="6">
         <v>65</v>
@@ -3966,13 +3966,13 @@
         <v>59</v>
       </c>
       <c r="G86" s="59" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H86" s="22"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="25" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B87" s="6">
         <v>65</v>
@@ -3992,10 +3992,10 @@
     </row>
     <row r="88" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="A88" s="30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="6">
@@ -4008,18 +4008,18 @@
         <v>59</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H88" s="40" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="25" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="6">
@@ -4036,10 +4036,10 @@
     </row>
     <row r="90" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A90" s="21" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="6">
@@ -4056,10 +4056,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="25" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="6">
@@ -4076,13 +4076,13 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D92" s="6">
         <v>0.9</v>
@@ -4095,18 +4095,18 @@
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="42" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="A93" s="29" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B93" s="6">
         <v>70</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D93" s="6">
         <v>0.8</v>
@@ -4119,12 +4119,12 @@
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="43" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="29" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B94" s="6">
         <v>77</v>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="24" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B95" s="6">
         <v>80</v>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="40" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B96" s="6">
         <v>80</v>
@@ -4185,15 +4185,15 @@
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="39" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A97" s="21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="6">
@@ -4210,10 +4210,10 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="6">
@@ -4230,13 +4230,13 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="29" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D99" s="6">
         <v>0.9</v>
@@ -4249,18 +4249,18 @@
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="29" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D100" s="6">
         <v>0.9</v>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B101" s="6">
         <v>83</v>
@@ -4293,15 +4293,15 @@
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="24" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="28" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C102" s="10"/>
       <c r="D102" s="6">
@@ -4315,15 +4315,15 @@
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="24" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="44" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="6">
@@ -4340,7 +4340,7 @@
     </row>
     <row r="104" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B104" s="6">
         <v>90</v>
@@ -4356,13 +4356,13 @@
         <v>29</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H104" s="22"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B105" s="6">
         <v>90</v>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="29" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B106" s="6">
         <v>90</v>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="24" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="29" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B107" s="6">
         <v>90</v>
@@ -4423,12 +4423,12 @@
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="24" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="29" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B108" s="6">
         <v>90</v>
@@ -4445,15 +4445,15 @@
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="29" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="6">
@@ -4467,18 +4467,18 @@
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="24" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="45" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B110" s="6">
         <v>95</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D110" s="6">
         <v>1</v>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="46" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="29" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B111" s="6">
         <v>95</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="29" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B112" s="6">
         <v>98</v>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="39" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="29" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B113" s="6">
         <v>100</v>
@@ -4557,12 +4557,12 @@
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="29" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B114" s="6">
         <v>100</v>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="29" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B115" s="6">
         <v>100</v>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="46" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="29" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B116" s="6">
         <v>100</v>
@@ -4623,18 +4623,18 @@
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="39" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A117" s="29" t="s">
+        <v>237</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C117" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="D117" s="6">
         <v>0.8</v>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="24" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B118" s="6">
         <v>100</v>
@@ -4669,15 +4669,15 @@
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="29" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="6">
@@ -4691,15 +4691,15 @@
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="34" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="29" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C120" s="10"/>
       <c r="D120" s="6">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="24" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="29" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B121" s="6">
         <v>100</v>
@@ -4735,18 +4735,18 @@
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="29" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B122" s="6">
         <v>105</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D122" s="6">
         <v>0.8</v>
@@ -4759,18 +4759,18 @@
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="39" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="29" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B123" s="6">
         <v>105</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D123" s="6">
         <v>0.7</v>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="39" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="28" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B124" s="6">
         <v>107</v>
@@ -4805,12 +4805,12 @@
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="34" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="29" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B125" s="6">
         <v>110</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="24" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="29" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B126" s="6">
         <v>110</v>
@@ -4849,12 +4849,12 @@
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="34" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="29" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B127" s="6">
         <v>110</v>
@@ -4871,12 +4871,12 @@
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="34" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="29" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B128" s="6">
         <v>112</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="29" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B129" s="6">
         <v>120</v>
@@ -4915,15 +4915,15 @@
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="24" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="B130" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="C130" s="10"/>
       <c r="D130" s="6">
@@ -4936,15 +4936,15 @@
         <v>50</v>
       </c>
       <c r="G130" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H130" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="29" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B131" s="6">
         <v>128</v>
@@ -4961,18 +4961,18 @@
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="47" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D132" s="6">
         <v>1</v>
@@ -4985,15 +4985,15 @@
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="40" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="29" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="6">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="40" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="29" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B134" s="6">
         <v>130</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="34" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="29" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B135" s="6">
         <v>132</v>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="39" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="29" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B136" s="6">
         <v>132</v>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="39" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="29" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B137" s="6">
         <v>132</v>
@@ -5095,15 +5095,15 @@
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="39" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="54" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B138" s="55" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C138" s="56"/>
       <c r="D138" s="55">
@@ -5117,15 +5117,15 @@
       </c>
       <c r="G138" s="57"/>
       <c r="H138" s="58" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="50" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C139" s="51"/>
       <c r="D139" s="15">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="G139" s="52"/>
       <c r="H139" s="53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -5151,15 +5151,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -5378,6 +5369,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5387,14 +5387,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5409,6 +5401,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -5151,6 +5151,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -5369,15 +5378,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5387,6 +5387,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5401,14 +5409,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718C23A5-8CB9-42F9-872B-D09AF11BB725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E30F886-FCE8-4C02-BCB6-0CC031C0C7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="332">
   <si>
     <t>武器</t>
   </si>
@@ -312,9 +312,6 @@
   </si>
   <si>
     <t>20 火伤</t>
-  </si>
-  <si>
-    <t>几率点燃敌人（5火伤*5下）；吓退夜游神</t>
   </si>
   <si>
     <t>冰弓</t>
@@ -944,9 +941,6 @@
     <t>衰败之弓</t>
   </si>
   <si>
-    <t>狼和恐狼对受影响的目标造成更多伤害</t>
-  </si>
-  <si>
     <t>渡鸦之喙</t>
   </si>
   <si>
@@ -956,9 +950,6 @@
     <t>双发弩</t>
   </si>
   <si>
-    <t>无视护甲目标对远程武器所具有的额外防御</t>
-  </si>
-  <si>
     <t>铁斧</t>
   </si>
   <si>
@@ -968,9 +959,6 @@
     <t>血猎犬</t>
   </si>
   <si>
-    <t>26.6%击晕敌人；潜行不造成伤害</t>
-  </si>
-  <si>
     <t>屠宰者战斧</t>
   </si>
   <si>
@@ -1017,13 +1005,61 @@
   </si>
   <si>
     <t>原松木*2 绳子*2 亚麻纤维*3</t>
+  </si>
+  <si>
+    <t>远程武器</t>
+  </si>
+  <si>
+    <t>几率点燃敌人（5火伤*5下）；吓退夜游神；远程武器</t>
+  </si>
+  <si>
+    <t>狼和恐狼对受影响的目标造成更多伤害；远程武器</t>
+  </si>
+  <si>
+    <t>减慢对手的攻击与奔跑速度；远程武器</t>
+  </si>
+  <si>
+    <t>26.6%击晕敌人；潜行不造成伤害；远程武器</t>
+  </si>
+  <si>
+    <t>潜行时可造成三倍伤害；远程武器</t>
+  </si>
+  <si>
+    <t>无视护甲目标对远程武器所具有的额外防御；远程武器</t>
+  </si>
+  <si>
+    <t>投掷药水</t>
+  </si>
+  <si>
+    <t>南瓜炸弹</t>
+  </si>
+  <si>
+    <t>冰冻药水</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>120 毒伤</t>
+  </si>
+  <si>
+    <t>对受影响的敌人造成恐惧，并造成35点伤害；远程武器</t>
+  </si>
+  <si>
+    <t>暂时冻结受影响的敌人，并造成20点伤害；远程武器</t>
+  </si>
+  <si>
+    <t>让受影响的敌人中毒，18秒内造成120点伤害；远程武器：炼金卓制作，且概率失败变为蘑菇浸剂</t>
+  </si>
+  <si>
+    <t>墓地蘑菇：20；艾莎眼泪：2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1097,8 +1133,28 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="serif"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1189,8 +1245,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1264,17 +1326,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1499,13 +1550,194 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1549,140 +1781,185 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2027,8 +2304,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396CB4A7-922E-403D-B02B-B84252EDCF5F}">
-  <dimension ref="A1:L139"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L142"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.796875" customWidth="1"/>
     <col min="2" max="2" width="16.46484375" customWidth="1"/>
@@ -2037,46 +2314,46 @@
     <col min="8" max="8" width="47.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21.4" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="60" t="s">
-        <v>291</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+    <row r="1" spans="1:12" ht="21.4" thickBot="1">
+      <c r="A1" s="73" t="s">
+        <v>290</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:12" ht="13.9">
+      <c r="A3" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2091,10 +2368,10 @@
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="22"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="H3" s="21"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="22" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2113,14 +2390,14 @@
         <v>13</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H4" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="H4" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:12" ht="13.9">
+      <c r="A5" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1">
@@ -2139,12 +2416,12 @@
       <c r="G5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+    <row r="6" spans="1:12">
+      <c r="A6" s="24" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="1">
@@ -2163,12 +2440,12 @@
       <c r="G6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:12" ht="13.9">
+      <c r="A7" s="20" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="1">
@@ -2187,12 +2464,12 @@
       <c r="G7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
+    <row r="8" spans="1:12">
+      <c r="A8" s="25" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="1">
@@ -2211,12 +2488,12 @@
       <c r="G8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:12" ht="13.9">
+      <c r="A9" s="20" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="1">
@@ -2235,12 +2512,12 @@
       <c r="G9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="23" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:12" ht="13.9">
+      <c r="A10" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -2257,10 +2534,10 @@
         <v>112</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="22"/>
-    </row>
-    <row r="11" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
+      <c r="H10" s="21"/>
+    </row>
+    <row r="11" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A11" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="1">
@@ -2279,12 +2556,12 @@
       <c r="G11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="23" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:12" ht="14.25" thickBot="1">
+      <c r="A12" s="20" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -2303,11 +2580,11 @@
       <c r="G12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="24"/>
-      <c r="L12" s="48"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="H12" s="23"/>
+      <c r="L12" s="46"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="24" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -2326,12 +2603,12 @@
       <c r="G13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="23" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A14" s="21" t="s">
+    <row r="14" spans="1:12" ht="13.9">
+      <c r="A14" s="20" t="s">
         <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -2348,11 +2625,11 @@
         <v>125</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="22"/>
-    </row>
-    <row r="15" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A15" s="27" t="s">
-        <v>301</v>
+      <c r="H14" s="21"/>
+    </row>
+    <row r="15" spans="1:12" ht="13.9">
+      <c r="A15" s="26" t="s">
+        <v>298</v>
       </c>
       <c r="B15" s="1">
         <v>18</v>
@@ -2368,14 +2645,14 @@
         <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A16" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="13.9">
+      <c r="A16" s="20" t="s">
         <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -2392,10 +2669,10 @@
         <v>77</v>
       </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="22"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
+      <c r="H16" s="21"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="24" t="s">
         <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -2412,10 +2689,10 @@
         <v>340</v>
       </c>
       <c r="G17" s="2"/>
-      <c r="H17" s="22"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="25" t="s">
+      <c r="H17" s="21"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="24" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -2434,12 +2711,12 @@
         <v>100</v>
       </c>
       <c r="G18" s="2"/>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="25" t="s">
+    <row r="19" spans="1:8">
+      <c r="A19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -2458,12 +2735,12 @@
         <v>13</v>
       </c>
       <c r="G19" s="2"/>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A20" s="25" t="s">
+    <row r="20" spans="1:8" ht="14.65">
+      <c r="A20" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -2482,12 +2759,12 @@
         <v>77</v>
       </c>
       <c r="G20" s="2"/>
-      <c r="H20" s="24" t="s">
+      <c r="H20" s="23" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A21" s="21" t="s">
+    <row r="21" spans="1:8" ht="13.9">
+      <c r="A21" s="20" t="s">
         <v>53</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -2504,12 +2781,12 @@
         <v>84</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H21" s="22"/>
-    </row>
-    <row r="22" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A22" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="H21" s="21"/>
+    </row>
+    <row r="22" spans="1:8" ht="13.9">
+      <c r="A22" s="20" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -2528,10 +2805,10 @@
       <c r="G22" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H22" s="22"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
+      <c r="H22" s="21"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="24" t="s">
         <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -2548,34 +2825,34 @@
         <v>500</v>
       </c>
       <c r="G23" s="2"/>
-      <c r="H23" s="22"/>
-    </row>
-    <row r="24" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A24" s="27" t="s">
-        <v>300</v>
+      <c r="H23" s="21"/>
+    </row>
+    <row r="24" spans="1:8" ht="13.9">
+      <c r="A24" s="26" t="s">
+        <v>297</v>
       </c>
       <c r="B24" s="1">
         <v>20</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="16">
+      <c r="D24" s="15">
         <v>1</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="15">
         <v>1.2</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="15">
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A25" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="13.9">
+      <c r="A25" s="20" t="s">
         <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -2592,14 +2869,14 @@
         <v>84</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H25" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="H25" s="23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="28" t="s">
+    <row r="26" spans="1:8">
+      <c r="A26" s="27" t="s">
         <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2616,12 +2893,12 @@
         <v>112</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="24" t="s">
+      <c r="H26" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A27" s="21" t="s">
+    <row r="27" spans="1:8" ht="13.9">
+      <c r="A27" s="20" t="s">
         <v>62</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -2640,12 +2917,12 @@
       <c r="G27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H27" s="24" t="s">
+      <c r="H27" s="23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A28" s="21" t="s">
+    <row r="28" spans="1:8" ht="13.9">
+      <c r="A28" s="20" t="s">
         <v>65</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -2664,12 +2941,12 @@
       <c r="G28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A29" s="21" t="s">
+    <row r="29" spans="1:8" ht="13.9">
+      <c r="A29" s="20" t="s">
         <v>66</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -2688,10 +2965,10 @@
       <c r="G29" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H29" s="22"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="29" t="s">
+      <c r="H29" s="21"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="28" t="s">
         <v>69</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -2708,12 +2985,12 @@
         <v>91</v>
       </c>
       <c r="G30" s="2"/>
-      <c r="H30" s="24" t="s">
+      <c r="H30" s="23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+    <row r="31" spans="1:8">
+      <c r="A31" s="29" t="s">
         <v>71</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -2730,10 +3007,10 @@
         <v>72</v>
       </c>
       <c r="G31" s="2"/>
-      <c r="H31" s="22"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
+      <c r="H31" s="21"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="24" t="s">
         <v>73</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -2750,10 +3027,10 @@
         <v>250</v>
       </c>
       <c r="G32" s="2"/>
-      <c r="H32" s="22"/>
-    </row>
-    <row r="33" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A33" s="31" t="s">
+      <c r="H32" s="21"/>
+    </row>
+    <row r="33" spans="1:8" ht="13.9">
+      <c r="A33" s="30" t="s">
         <v>74</v>
       </c>
       <c r="B33" s="6">
@@ -2772,10 +3049,12 @@
       <c r="G33" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H33" s="22"/>
-    </row>
-    <row r="34" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A34" s="21" t="s">
+      <c r="H33" s="21" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="13.9">
+      <c r="A34" s="20" t="s">
         <v>76</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -2794,10 +3073,10 @@
       <c r="G34" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H34" s="22"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
+      <c r="H34" s="21"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="24" t="s">
         <v>79</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -2814,10 +3093,10 @@
         <v>250</v>
       </c>
       <c r="G35" s="2"/>
-      <c r="H35" s="22"/>
-    </row>
-    <row r="36" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A36" s="21" t="s">
+      <c r="H35" s="21"/>
+    </row>
+    <row r="36" spans="1:8" ht="13.9">
+      <c r="A36" s="20" t="s">
         <v>80</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -2836,12 +3115,12 @@
       <c r="G36" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="24" t="s">
+      <c r="H36" s="23" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A37" s="21" t="s">
+    <row r="37" spans="1:8" ht="13.9">
+      <c r="A37" s="20" t="s">
         <v>83</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -2860,12 +3139,12 @@
       <c r="G37" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H37" s="24" t="s">
+      <c r="H37" s="23" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A38" s="21" t="s">
+    <row r="38" spans="1:8" ht="13.9">
+      <c r="A38" s="20" t="s">
         <v>84</v>
       </c>
       <c r="B38" s="6">
@@ -2882,10 +3161,10 @@
         <v>50</v>
       </c>
       <c r="G38" s="2"/>
-      <c r="H38" s="22"/>
-    </row>
-    <row r="39" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A39" s="21" t="s">
+      <c r="H38" s="21"/>
+    </row>
+    <row r="39" spans="1:8" ht="13.9">
+      <c r="A39" s="20" t="s">
         <v>85</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -2904,12 +3183,12 @@
       <c r="G39" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H39" s="24" t="s">
+      <c r="H39" s="23" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
+    <row r="40" spans="1:8">
+      <c r="A40" s="24" t="s">
         <v>88</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -2928,12 +3207,12 @@
       <c r="G40" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H40" s="24" t="s">
+      <c r="H40" s="23" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="28" t="s">
+    <row r="41" spans="1:8">
+      <c r="A41" s="27" t="s">
         <v>90</v>
       </c>
       <c r="B41" s="6">
@@ -2952,19 +3231,19 @@
         <v>46</v>
       </c>
       <c r="G41" s="2"/>
-      <c r="H41" s="24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A42" s="32" t="s">
-        <v>294</v>
+      <c r="H41" s="23" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="14.65">
+      <c r="A42" s="31" t="s">
+        <v>293</v>
       </c>
       <c r="B42" s="6">
         <v>30</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D42" s="6">
         <v>0.8</v>
@@ -2976,19 +3255,19 @@
         <v>46</v>
       </c>
       <c r="G42" s="2"/>
-      <c r="H42" s="24" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="33" t="s">
-        <v>93</v>
+      <c r="H42" s="23" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="32" t="s">
+        <v>92</v>
       </c>
       <c r="B43" s="6">
         <v>30</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D43" s="6">
         <v>0.8</v>
@@ -3000,16 +3279,16 @@
         <v>56</v>
       </c>
       <c r="G43" s="2"/>
-      <c r="H43" s="24" t="s">
+      <c r="H43" s="23" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="13.9">
+      <c r="A44" s="20" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A44" s="21" t="s">
+      <c r="B44" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="6">
@@ -3022,16 +3301,16 @@
         <v>67</v>
       </c>
       <c r="G44" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H44" s="21"/>
+    </row>
+    <row r="45" spans="1:8" ht="13.9">
+      <c r="A45" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="H44" s="22"/>
-    </row>
-    <row r="45" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A45" s="21" t="s">
+      <c r="B45" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="6">
@@ -3044,18 +3323,18 @@
         <v>67</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H45" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="H45" s="23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="13.9">
+      <c r="A46" s="20" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A46" s="21" t="s">
+      <c r="B46" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="6">
@@ -3068,13 +3347,13 @@
         <v>77</v>
       </c>
       <c r="G46" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="24" t="s">
         <v>104</v>
-      </c>
-      <c r="H46" s="22"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="25" t="s">
-        <v>105</v>
       </c>
       <c r="B47" s="6">
         <v>35</v>
@@ -3090,14 +3369,16 @@
         <v>59</v>
       </c>
       <c r="G47" s="2"/>
-      <c r="H47" s="22"/>
-    </row>
-    <row r="48" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A48" s="21" t="s">
+      <c r="H47" s="21" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="13.9">
+      <c r="A48" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="6">
@@ -3110,16 +3391,16 @@
         <v>84</v>
       </c>
       <c r="G48" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H48" s="21"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.9">
+      <c r="A49" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="H48" s="22"/>
-    </row>
-    <row r="49" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A49" s="21" t="s">
+      <c r="B49" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="6">
@@ -3132,16 +3413,16 @@
         <v>91</v>
       </c>
       <c r="G49" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H49" s="21"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.9">
+      <c r="A50" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="H49" s="22"/>
-    </row>
-    <row r="50" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A50" s="21" t="s">
+      <c r="B50" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="6">
@@ -3154,18 +3435,18 @@
         <v>77</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H50" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="H50" s="23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="13.9">
+      <c r="A51" s="20" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A51" s="21" t="s">
-        <v>115</v>
-      </c>
       <c r="B51" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="6">
@@ -3178,18 +3459,18 @@
         <v>77</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H51" s="24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A52" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H51" s="23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="13.9">
+      <c r="A52" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="6">
@@ -3202,18 +3483,18 @@
         <v>84</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H52" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="H52" s="23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="13.9">
+      <c r="A53" s="20" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A53" s="21" t="s">
+      <c r="B53" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="6">
@@ -3226,18 +3507,18 @@
         <v>91</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H53" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="H53" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="13.9">
+      <c r="A54" s="20" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A54" s="21" t="s">
-        <v>122</v>
-      </c>
       <c r="B54" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="6">
@@ -3250,15 +3531,15 @@
         <v>91</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H54" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="25" t="s">
-        <v>124</v>
+        <v>110</v>
+      </c>
+      <c r="H54" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="24" t="s">
+        <v>123</v>
       </c>
       <c r="B55" s="6">
         <v>42</v>
@@ -3274,14 +3555,14 @@
         <v>72</v>
       </c>
       <c r="G55" s="2"/>
-      <c r="H55" s="22"/>
-    </row>
-    <row r="56" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A56" s="21" t="s">
+      <c r="H55" s="21"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.9">
+      <c r="A56" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="6">
@@ -3294,16 +3575,16 @@
         <v>72</v>
       </c>
       <c r="G56" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H56" s="21"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="H56" s="22"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="25" t="s">
-        <v>128</v>
-      </c>
       <c r="B57" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="6">
@@ -3316,11 +3597,11 @@
         <v>100</v>
       </c>
       <c r="G57" s="2"/>
-      <c r="H57" s="22"/>
-    </row>
-    <row r="58" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A58" s="21" t="s">
-        <v>129</v>
+      <c r="H57" s="21"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.9">
+      <c r="A58" s="20" t="s">
+        <v>128</v>
       </c>
       <c r="B58" s="6">
         <v>45</v>
@@ -3336,16 +3617,18 @@
         <v>35</v>
       </c>
       <c r="G58" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H58" s="21" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="H58" s="22"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="28" t="s">
+      <c r="B59" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="6">
@@ -3358,16 +3641,16 @@
         <v>100</v>
       </c>
       <c r="G59" s="2"/>
-      <c r="H59" s="34" t="s">
+      <c r="H59" s="33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="28" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="29" t="s">
+      <c r="B60" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="6">
@@ -3380,19 +3663,19 @@
         <v>67</v>
       </c>
       <c r="G60" s="2"/>
-      <c r="H60" s="34" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A61" s="29" t="s">
+      <c r="H60" s="33" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="14.65">
+      <c r="A61" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>290</v>
-      </c>
       <c r="C61" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D61" s="6">
         <v>1.5</v>
@@ -3404,19 +3687,19 @@
         <v>67</v>
       </c>
       <c r="G61" s="2"/>
-      <c r="H61" s="24" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A62" s="28" t="s">
-        <v>136</v>
+      <c r="H61" s="23" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="14.65">
+      <c r="A62" s="27" t="s">
+        <v>135</v>
       </c>
       <c r="B62" s="6">
         <v>50</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D62" s="6">
         <v>1</v>
@@ -3428,13 +3711,13 @@
         <v>50</v>
       </c>
       <c r="G62" s="2"/>
-      <c r="H62" s="24" t="s">
+      <c r="H62" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="27">
+      <c r="A63" s="27" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A63" s="28" t="s">
-        <v>139</v>
       </c>
       <c r="B63" s="6">
         <v>52</v>
@@ -3450,13 +3733,13 @@
         <v>91</v>
       </c>
       <c r="G63" s="2"/>
-      <c r="H63" s="35" t="s">
+      <c r="H63" s="34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="25.9" customHeight="1">
+      <c r="A64" s="35" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="36" t="s">
-        <v>141</v>
       </c>
       <c r="B64" s="6">
         <v>55</v>
@@ -3472,13 +3755,15 @@
         <v>35</v>
       </c>
       <c r="G64" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H64" s="53" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="27" customHeight="1">
+      <c r="A65" s="27" t="s">
         <v>142</v>
-      </c>
-      <c r="H64" s="37"/>
-    </row>
-    <row r="65" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="28" t="s">
-        <v>143</v>
       </c>
       <c r="B65" s="6">
         <v>55</v>
@@ -3494,13 +3779,13 @@
         <v>77</v>
       </c>
       <c r="G65" s="2"/>
-      <c r="H65" s="24" t="s">
+      <c r="H65" s="23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="27" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="28" t="s">
-        <v>145</v>
       </c>
       <c r="B66" s="6">
         <v>55</v>
@@ -3518,16 +3803,16 @@
         <v>67</v>
       </c>
       <c r="G66" s="2"/>
-      <c r="H66" s="24" t="s">
+      <c r="H66" s="23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="27" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="28" t="s">
+      <c r="B67" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="6">
@@ -3540,16 +3825,16 @@
         <v>67</v>
       </c>
       <c r="G67" s="2"/>
-      <c r="H67" s="24" t="s">
+      <c r="H67" s="23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="27" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="28" t="s">
-        <v>150</v>
-      </c>
       <c r="B68" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="6">
@@ -3562,16 +3847,16 @@
         <v>91</v>
       </c>
       <c r="G68" s="2"/>
-      <c r="H68" s="24" t="s">
+      <c r="H68" s="23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="27">
+      <c r="A69" s="36" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A69" s="38" t="s">
+      <c r="B69" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="6">
@@ -3584,16 +3869,16 @@
         <v>56</v>
       </c>
       <c r="G69" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H69" s="21"/>
+    </row>
+    <row r="70" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A70" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="H69" s="22"/>
-    </row>
-    <row r="70" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="21" t="s">
+      <c r="B70" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="6">
@@ -3606,14 +3891,14 @@
         <v>72</v>
       </c>
       <c r="G70" s="2"/>
-      <c r="H70" s="22"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="25" t="s">
-        <v>157</v>
+      <c r="H70" s="21"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="6">
@@ -3626,11 +3911,11 @@
         <v>100</v>
       </c>
       <c r="G71" s="2"/>
-      <c r="H71" s="22"/>
-    </row>
-    <row r="72" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="29" t="s">
-        <v>158</v>
+      <c r="H71" s="21"/>
+    </row>
+    <row r="72" spans="1:8" ht="44.25" customHeight="1">
+      <c r="A72" s="28" t="s">
+        <v>157</v>
       </c>
       <c r="B72" s="6">
         <v>60</v>
@@ -3646,16 +3931,16 @@
         <v>56</v>
       </c>
       <c r="G72" s="2"/>
-      <c r="H72" s="39" t="s">
+      <c r="H72" s="37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="21" customHeight="1">
+      <c r="A73" s="27" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="28" t="s">
+      <c r="B73" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="6">
@@ -3668,14 +3953,14 @@
         <v>84</v>
       </c>
       <c r="G73" s="2"/>
-      <c r="H73" s="22"/>
-    </row>
-    <row r="74" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A74" s="29" t="s">
+      <c r="H73" s="21"/>
+    </row>
+    <row r="74" spans="1:8" ht="40.5">
+      <c r="A74" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="6">
@@ -3688,19 +3973,19 @@
         <v>77</v>
       </c>
       <c r="G74" s="2"/>
-      <c r="H74" s="39" t="s">
+      <c r="H74" s="37" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="44.65" customHeight="1">
+      <c r="A75" s="27" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="44.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="28" t="s">
-        <v>165</v>
       </c>
       <c r="B75" s="6">
         <v>60</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D75" s="6">
         <v>1</v>
@@ -3712,19 +3997,19 @@
         <v>63</v>
       </c>
       <c r="G75" s="2"/>
-      <c r="H75" s="40" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="28" t="s">
-        <v>167</v>
+      <c r="H75" s="38" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="27" t="s">
+        <v>166</v>
       </c>
       <c r="B76" s="6">
         <v>60</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D76" s="6">
         <v>0.9</v>
@@ -3736,19 +4021,19 @@
         <v>56</v>
       </c>
       <c r="G76" s="2"/>
-      <c r="H76" s="24" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A77" s="28" t="s">
-        <v>313</v>
+      <c r="H76" s="23" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="14.25">
+      <c r="A77" s="27" t="s">
+        <v>309</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D77" s="6">
         <v>0.9</v>
@@ -3760,19 +4045,19 @@
         <v>56</v>
       </c>
       <c r="G77" s="2"/>
-      <c r="H77" s="24" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="28" t="s">
-        <v>169</v>
+      <c r="H77" s="23" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="27" t="s">
+        <v>168</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D78" s="6">
         <v>1.1000000000000001</v>
@@ -3784,19 +4069,19 @@
         <v>53</v>
       </c>
       <c r="G78" s="2"/>
-      <c r="H78" s="24" t="s">
+      <c r="H78" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="27" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="28" t="s">
+      <c r="B79" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>172</v>
       </c>
       <c r="D79" s="6">
         <v>1.1000000000000001</v>
@@ -3808,16 +4093,16 @@
         <v>59</v>
       </c>
       <c r="G79" s="2"/>
-      <c r="H79" s="24" t="s">
+      <c r="H79" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="27">
+      <c r="A80" s="20" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" ht="27" x14ac:dyDescent="0.35">
-      <c r="A80" s="21" t="s">
+      <c r="B80" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="6">
@@ -3830,13 +4115,13 @@
         <v>59</v>
       </c>
       <c r="G80" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H80" s="39"/>
+    </row>
+    <row r="81" spans="1:8" ht="28.9" customHeight="1">
+      <c r="A81" s="27" t="s">
         <v>176</v>
-      </c>
-      <c r="H80" s="41"/>
-    </row>
-    <row r="81" spans="1:8" ht="28.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="28" t="s">
-        <v>177</v>
       </c>
       <c r="B81" s="6">
         <v>62</v>
@@ -3852,16 +4137,16 @@
         <v>67</v>
       </c>
       <c r="G81" s="2"/>
-      <c r="H81" s="39" t="s">
+      <c r="H81" s="37" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="33" customHeight="1">
+      <c r="A82" s="29" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="30" t="s">
+      <c r="B82" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="6">
@@ -3874,18 +4159,18 @@
         <v>56</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="H82" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="H82" s="38" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="27.4" customHeight="1">
+      <c r="A83" s="20" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" ht="27.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="21" t="s">
-        <v>182</v>
-      </c>
       <c r="B83" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="6">
@@ -3898,18 +4183,18 @@
         <v>56</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="H83" s="40" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="H83" s="38" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A84" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="B84" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="6">
@@ -3922,16 +4207,16 @@
         <v>56</v>
       </c>
       <c r="G84" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H84" s="21"/>
+    </row>
+    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+      <c r="A85" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="H84" s="22"/>
-    </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="29" t="s">
+      <c r="B85" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="6">
@@ -3944,13 +4229,13 @@
         <v>67</v>
       </c>
       <c r="G85" s="2"/>
-      <c r="H85" s="39" t="s">
+      <c r="H85" s="37" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="30.75" customHeight="1">
+      <c r="A86" s="24" t="s">
         <v>188</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="25" t="s">
-        <v>189</v>
       </c>
       <c r="B86" s="6">
         <v>65</v>
@@ -3965,14 +4250,16 @@
       <c r="F86" s="6">
         <v>59</v>
       </c>
-      <c r="G86" s="59" t="s">
-        <v>317</v>
-      </c>
-      <c r="H86" s="22"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="25" t="s">
-        <v>190</v>
+      <c r="G86" s="52" t="s">
+        <v>313</v>
+      </c>
+      <c r="H86" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="24" t="s">
+        <v>189</v>
       </c>
       <c r="B87" s="6">
         <v>65</v>
@@ -3988,14 +4275,16 @@
         <v>84</v>
       </c>
       <c r="G87" s="2"/>
-      <c r="H87" s="22"/>
-    </row>
-    <row r="88" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A88" s="30" t="s">
+      <c r="H87" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="27">
+      <c r="A88" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="6">
@@ -4008,18 +4297,18 @@
         <v>59</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="H88" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="H88" s="38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="30.4" customHeight="1">
+      <c r="A89" s="24" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="25" t="s">
-        <v>194</v>
-      </c>
       <c r="B89" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="6">
@@ -4032,14 +4321,14 @@
         <v>84</v>
       </c>
       <c r="G89" s="2"/>
-      <c r="H89" s="22"/>
-    </row>
-    <row r="90" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A90" s="21" t="s">
+      <c r="H89" s="21"/>
+    </row>
+    <row r="90" spans="1:8" ht="13.9">
+      <c r="A90" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="6">
@@ -4052,14 +4341,14 @@
         <v>63</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="22"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="25" t="s">
-        <v>197</v>
+      <c r="H90" s="21"/>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="24" t="s">
+        <v>196</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="6">
@@ -4072,17 +4361,17 @@
         <v>91</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="22"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="29" t="s">
+      <c r="H91" s="21"/>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C92" s="8" t="s">
         <v>198</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>199</v>
       </c>
       <c r="D92" s="6">
         <v>0.9</v>
@@ -4094,19 +4383,19 @@
         <v>46</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="42" t="s">
+      <c r="H92" s="40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="27">
+      <c r="A93" s="28" t="s">
         <v>200</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A93" s="29" t="s">
-        <v>201</v>
       </c>
       <c r="B93" s="6">
         <v>70</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D93" s="6">
         <v>0.8</v>
@@ -4118,13 +4407,13 @@
         <v>72</v>
       </c>
       <c r="G93" s="2"/>
-      <c r="H93" s="43" t="s">
+      <c r="H93" s="41" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="28" t="s">
         <v>203</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="29" t="s">
-        <v>204</v>
       </c>
       <c r="B94" s="6">
         <v>77</v>
@@ -4140,13 +4429,13 @@
         <v>72</v>
       </c>
       <c r="G94" s="2"/>
-      <c r="H94" s="24" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="28" t="s">
-        <v>123</v>
+      <c r="H94" s="23" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="27" t="s">
+        <v>122</v>
       </c>
       <c r="B95" s="6">
         <v>80</v>
@@ -4162,13 +4451,13 @@
         <v>100</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="40" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="29" t="s">
-        <v>206</v>
+      <c r="H95" s="38" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="30.75" customHeight="1">
+      <c r="A96" s="28" t="s">
+        <v>205</v>
       </c>
       <c r="B96" s="6">
         <v>80</v>
@@ -4184,16 +4473,16 @@
         <v>50</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="39" t="s">
+      <c r="H96" s="37" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="13.9">
+      <c r="A97" s="20" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A97" s="21" t="s">
+      <c r="B97" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="6">
@@ -4206,14 +4495,14 @@
         <v>46</v>
       </c>
       <c r="G97" s="2"/>
-      <c r="H97" s="22"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="25" t="s">
-        <v>210</v>
+      <c r="H97" s="21"/>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="24" t="s">
+        <v>209</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="6">
@@ -4226,17 +4515,17 @@
         <v>63</v>
       </c>
       <c r="G98" s="2"/>
-      <c r="H98" s="22"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="29" t="s">
+      <c r="H98" s="21"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C99" s="7" t="s">
         <v>211</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>212</v>
       </c>
       <c r="D99" s="6">
         <v>0.9</v>
@@ -4248,19 +4537,19 @@
         <v>46</v>
       </c>
       <c r="G99" s="2"/>
-      <c r="H99" s="24" t="s">
+      <c r="H99" s="23" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="28" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="29" t="s">
+      <c r="B100" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C100" s="8" t="s">
         <v>214</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>215</v>
       </c>
       <c r="D100" s="6">
         <v>0.9</v>
@@ -4272,11 +4561,11 @@
         <v>46</v>
       </c>
       <c r="G100" s="3"/>
-      <c r="H100" s="24"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="29" t="s">
-        <v>216</v>
+      <c r="H100" s="23"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="28" t="s">
+        <v>215</v>
       </c>
       <c r="B101" s="6">
         <v>83</v>
@@ -4292,16 +4581,16 @@
         <v>72</v>
       </c>
       <c r="G101" s="2"/>
-      <c r="H101" s="24" t="s">
+      <c r="H101" s="23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="27" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="28" t="s">
+      <c r="B102" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="C102" s="10"/>
       <c r="D102" s="6">
@@ -4314,16 +4603,16 @@
         <v>56</v>
       </c>
       <c r="G102" s="2"/>
-      <c r="H102" s="24" t="s">
+      <c r="H102" s="23" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="42" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="44" t="s">
+      <c r="B103" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="6">
@@ -4336,11 +4625,11 @@
         <v>56</v>
       </c>
       <c r="G103" s="2"/>
-      <c r="H103" s="22"/>
-    </row>
-    <row r="104" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="25" t="s">
-        <v>223</v>
+      <c r="H103" s="21"/>
+    </row>
+    <row r="104" spans="1:8" ht="31.5" customHeight="1">
+      <c r="A104" s="24" t="s">
+        <v>222</v>
       </c>
       <c r="B104" s="6">
         <v>90</v>
@@ -4356,13 +4645,15 @@
         <v>29</v>
       </c>
       <c r="G104" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="H104" s="54" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="27" t="s">
         <v>224</v>
-      </c>
-      <c r="H104" s="22"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="28" t="s">
-        <v>225</v>
       </c>
       <c r="B105" s="6">
         <v>90</v>
@@ -4378,13 +4669,13 @@
         <v>50</v>
       </c>
       <c r="G105" s="2"/>
-      <c r="H105" s="24" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="29" t="s">
-        <v>302</v>
+      <c r="H105" s="23" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="28" t="s">
+        <v>299</v>
       </c>
       <c r="B106" s="6">
         <v>90</v>
@@ -4400,13 +4691,13 @@
         <v>67</v>
       </c>
       <c r="G106" s="2"/>
-      <c r="H106" s="24" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="29" t="s">
-        <v>309</v>
+      <c r="H106" s="23" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="28" t="s">
+        <v>305</v>
       </c>
       <c r="B107" s="6">
         <v>90</v>
@@ -4422,13 +4713,13 @@
         <v>90</v>
       </c>
       <c r="G107" s="2"/>
-      <c r="H107" s="24" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="29" t="s">
-        <v>227</v>
+      <c r="H107" s="23" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="28" t="s">
+        <v>226</v>
       </c>
       <c r="B108" s="6">
         <v>90</v>
@@ -4444,16 +4735,16 @@
         <v>56</v>
       </c>
       <c r="G108" s="2"/>
-      <c r="H108" s="24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="29" t="s">
+      <c r="H108" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="B109" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="6">
@@ -4466,19 +4757,19 @@
         <v>77</v>
       </c>
       <c r="G109" s="2"/>
-      <c r="H109" s="24" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="45" t="s">
-        <v>286</v>
+      <c r="H109" s="23" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="31.9" customHeight="1">
+      <c r="A110" s="43" t="s">
+        <v>285</v>
       </c>
       <c r="B110" s="6">
         <v>95</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D110" s="6">
         <v>1</v>
@@ -4490,13 +4781,13 @@
         <v>46</v>
       </c>
       <c r="G110" s="2"/>
-      <c r="H110" s="46" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="29" t="s">
-        <v>231</v>
+      <c r="H110" s="44" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="30.75" customHeight="1">
+      <c r="A111" s="28" t="s">
+        <v>230</v>
       </c>
       <c r="B111" s="6">
         <v>95</v>
@@ -4512,13 +4803,13 @@
         <v>40</v>
       </c>
       <c r="G111" s="2"/>
-      <c r="H111" s="39" t="s">
+      <c r="H111" s="37" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A112" s="28" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="29" t="s">
-        <v>233</v>
       </c>
       <c r="B112" s="6">
         <v>98</v>
@@ -4534,13 +4825,13 @@
         <v>100</v>
       </c>
       <c r="G112" s="2"/>
-      <c r="H112" s="39" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="29" t="s">
-        <v>304</v>
+      <c r="H112" s="37" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A113" s="28" t="s">
+        <v>300</v>
       </c>
       <c r="B113" s="6">
         <v>100</v>
@@ -4556,13 +4847,13 @@
         <v>50</v>
       </c>
       <c r="G113" s="2"/>
-      <c r="H113" s="39" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="29" t="s">
-        <v>308</v>
+      <c r="H113" s="37" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A114" s="28" t="s">
+        <v>304</v>
       </c>
       <c r="B114" s="6">
         <v>100</v>
@@ -4578,13 +4869,13 @@
         <v>72</v>
       </c>
       <c r="G114" s="2"/>
-      <c r="H114" s="39" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="29" t="s">
-        <v>296</v>
+      <c r="H114" s="37" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A115" s="28" t="s">
+        <v>294</v>
       </c>
       <c r="B115" s="6">
         <v>100</v>
@@ -4600,13 +4891,13 @@
         <v>100</v>
       </c>
       <c r="G115" s="2"/>
-      <c r="H115" s="46" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="29" t="s">
-        <v>235</v>
+      <c r="H115" s="44" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="33" customHeight="1">
+      <c r="A116" s="28" t="s">
+        <v>234</v>
       </c>
       <c r="B116" s="6">
         <v>100</v>
@@ -4622,19 +4913,19 @@
         <v>50</v>
       </c>
       <c r="G116" s="2"/>
-      <c r="H116" s="39" t="s">
+      <c r="H116" s="37" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="14.65">
+      <c r="A117" s="28" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
-      <c r="A117" s="29" t="s">
+      <c r="B117" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B117" s="6" t="s">
+      <c r="C117" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="D117" s="6">
         <v>0.8</v>
@@ -4646,13 +4937,13 @@
         <v>46</v>
       </c>
       <c r="G117" s="2"/>
-      <c r="H117" s="24" t="s">
+      <c r="H117" s="23" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="28" t="s">
         <v>240</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="29" t="s">
-        <v>241</v>
       </c>
       <c r="B118" s="6">
         <v>100</v>
@@ -4668,16 +4959,16 @@
         <v>59</v>
       </c>
       <c r="G118" s="2"/>
-      <c r="H118" s="24" t="s">
+      <c r="H118" s="23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="28" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="29" t="s">
-        <v>243</v>
-      </c>
       <c r="B119" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="6">
@@ -4690,16 +4981,16 @@
         <v>72</v>
       </c>
       <c r="G119" s="2"/>
-      <c r="H119" s="34" t="s">
+      <c r="H119" s="33" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="28" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="29" t="s">
-        <v>245</v>
-      </c>
       <c r="B120" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C120" s="10"/>
       <c r="D120" s="6">
@@ -4712,13 +5003,13 @@
         <v>77</v>
       </c>
       <c r="G120" s="2"/>
-      <c r="H120" s="24" t="s">
+      <c r="H120" s="23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="28" t="s">
         <v>246</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="29" t="s">
-        <v>247</v>
       </c>
       <c r="B121" s="6">
         <v>100</v>
@@ -4734,19 +5025,19 @@
         <v>72</v>
       </c>
       <c r="G121" s="2"/>
-      <c r="H121" s="24" t="s">
+      <c r="H121" s="23" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="18.399999999999999" customHeight="1">
+      <c r="A122" s="28" t="s">
         <v>248</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="29" t="s">
-        <v>249</v>
       </c>
       <c r="B122" s="6">
         <v>105</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D122" s="6">
         <v>0.8</v>
@@ -4758,19 +5049,19 @@
         <v>46</v>
       </c>
       <c r="G122" s="2"/>
-      <c r="H122" s="39" t="s">
+      <c r="H122" s="37" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="31.15" customHeight="1">
+      <c r="A123" s="28" t="s">
         <v>251</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="29" t="s">
-        <v>252</v>
       </c>
       <c r="B123" s="6">
         <v>105</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D123" s="6">
         <v>0.7</v>
@@ -4782,13 +5073,13 @@
         <v>50</v>
       </c>
       <c r="G123" s="2"/>
-      <c r="H123" s="39" t="s">
+      <c r="H123" s="37" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="27" t="s">
         <v>253</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="28" t="s">
-        <v>254</v>
       </c>
       <c r="B124" s="6">
         <v>107</v>
@@ -4804,13 +5095,13 @@
         <v>67</v>
       </c>
       <c r="G124" s="2"/>
-      <c r="H124" s="34" t="s">
+      <c r="H124" s="33" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="28" t="s">
         <v>255</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="29" t="s">
-        <v>256</v>
       </c>
       <c r="B125" s="6">
         <v>110</v>
@@ -4826,13 +5117,13 @@
         <v>67</v>
       </c>
       <c r="G125" s="2"/>
-      <c r="H125" s="24" t="s">
+      <c r="H125" s="23" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="28" t="s">
         <v>257</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="29" t="s">
-        <v>258</v>
       </c>
       <c r="B126" s="6">
         <v>110</v>
@@ -4848,13 +5139,13 @@
         <v>67</v>
       </c>
       <c r="G126" s="2"/>
-      <c r="H126" s="34" t="s">
+      <c r="H126" s="33" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="28" t="s">
         <v>259</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="29" t="s">
-        <v>260</v>
       </c>
       <c r="B127" s="6">
         <v>110</v>
@@ -4870,13 +5161,13 @@
         <v>98</v>
       </c>
       <c r="G127" s="2"/>
-      <c r="H127" s="34" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="29" t="s">
-        <v>261</v>
+      <c r="H127" s="33" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="28" t="s">
+        <v>260</v>
       </c>
       <c r="B128" s="6">
         <v>112</v>
@@ -4892,13 +5183,13 @@
         <v>50</v>
       </c>
       <c r="G128" s="2"/>
-      <c r="H128" s="24" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="29" t="s">
-        <v>298</v>
+      <c r="H128" s="23" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="28" t="s">
+        <v>296</v>
       </c>
       <c r="B129" s="6">
         <v>120</v>
@@ -4914,16 +5205,16 @@
         <v>100</v>
       </c>
       <c r="G129" s="2"/>
-      <c r="H129" s="24" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="28" t="s">
-        <v>280</v>
+      <c r="H129" s="23" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="45.75" customHeight="1">
+      <c r="A130" s="27" t="s">
+        <v>279</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C130" s="10"/>
       <c r="D130" s="6">
@@ -4936,15 +5227,15 @@
         <v>50</v>
       </c>
       <c r="G130" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="H130" s="39" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" s="29" t="s">
-        <v>263</v>
+        <v>283</v>
+      </c>
+      <c r="H130" s="37" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="28" t="s">
+        <v>262</v>
       </c>
       <c r="B131" s="6">
         <v>128</v>
@@ -4960,19 +5251,19 @@
         <v>46</v>
       </c>
       <c r="G131" s="2"/>
-      <c r="H131" s="24" t="s">
+      <c r="H131" s="23" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="30" customHeight="1">
+      <c r="A132" s="45" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="47" t="s">
+      <c r="B132" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="B132" s="6" t="s">
-        <v>266</v>
-      </c>
       <c r="C132" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D132" s="6">
         <v>1</v>
@@ -4984,16 +5275,16 @@
         <v>53</v>
       </c>
       <c r="G132" s="2"/>
-      <c r="H132" s="40" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="29" t="s">
-        <v>278</v>
+      <c r="H132" s="38" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="17.649999999999999" customHeight="1">
+      <c r="A133" s="28" t="s">
+        <v>277</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="6">
@@ -5006,13 +5297,13 @@
         <v>46</v>
       </c>
       <c r="G133" s="2"/>
-      <c r="H133" s="40" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="29" t="s">
-        <v>268</v>
+      <c r="H133" s="38" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="28" t="s">
+        <v>267</v>
       </c>
       <c r="B134" s="6">
         <v>130</v>
@@ -5028,13 +5319,13 @@
         <v>50</v>
       </c>
       <c r="G134" s="2"/>
-      <c r="H134" s="34" t="s">
+      <c r="H134" s="33" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A135" s="28" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="29" t="s">
-        <v>270</v>
       </c>
       <c r="B135" s="6">
         <v>132</v>
@@ -5050,13 +5341,13 @@
         <v>50</v>
       </c>
       <c r="G135" s="2"/>
-      <c r="H135" s="39" t="s">
+      <c r="H135" s="37" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="34.5" customHeight="1">
+      <c r="A136" s="28" t="s">
         <v>271</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="29" t="s">
-        <v>272</v>
       </c>
       <c r="B136" s="6">
         <v>132</v>
@@ -5072,13 +5363,13 @@
         <v>46</v>
       </c>
       <c r="G136" s="2"/>
-      <c r="H136" s="39" t="s">
+      <c r="H136" s="37" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="33" customHeight="1">
+      <c r="A137" s="28" t="s">
         <v>273</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="29" t="s">
-        <v>274</v>
       </c>
       <c r="B137" s="6">
         <v>132</v>
@@ -5094,52 +5385,125 @@
         <v>63</v>
       </c>
       <c r="G137" s="2"/>
-      <c r="H137" s="39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A138" s="54" t="s">
+      <c r="H137" s="37" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="48" t="s">
+        <v>274</v>
+      </c>
+      <c r="B138" s="49" t="s">
         <v>275</v>
       </c>
-      <c r="B138" s="55" t="s">
+      <c r="C138" s="50"/>
+      <c r="D138" s="49">
+        <v>0.8</v>
+      </c>
+      <c r="E138" s="49">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F138" s="49">
+        <v>50</v>
+      </c>
+      <c r="G138" s="55"/>
+      <c r="H138" s="51" t="s">
         <v>276</v>
       </c>
-      <c r="C138" s="56"/>
-      <c r="D138" s="55">
-        <v>0.8</v>
-      </c>
-      <c r="E138" s="55">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F138" s="55">
-        <v>50</v>
-      </c>
-      <c r="G138" s="57"/>
-      <c r="H138" s="58" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="50" t="s">
-        <v>310</v>
-      </c>
-      <c r="B139" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="C139" s="51"/>
-      <c r="D139" s="15">
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="62" t="s">
+        <v>306</v>
+      </c>
+      <c r="B139" s="56" t="s">
+        <v>307</v>
+      </c>
+      <c r="C139" s="50"/>
+      <c r="D139" s="56">
         <v>1</v>
       </c>
-      <c r="E139" s="15">
+      <c r="E139" s="56">
         <v>2</v>
       </c>
-      <c r="F139" s="15">
+      <c r="F139" s="56">
         <v>143</v>
       </c>
-      <c r="G139" s="52"/>
-      <c r="H139" s="53" t="s">
-        <v>312</v>
+      <c r="G139" s="55"/>
+      <c r="H139" s="63" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="27">
+      <c r="A140" s="64" t="s">
+        <v>323</v>
+      </c>
+      <c r="B140" s="57" t="s">
+        <v>326</v>
+      </c>
+      <c r="C140" s="58" t="s">
+        <v>327</v>
+      </c>
+      <c r="D140" s="57" t="s">
+        <v>326</v>
+      </c>
+      <c r="E140" s="57">
+        <v>5</v>
+      </c>
+      <c r="F140" s="57">
+        <v>1</v>
+      </c>
+      <c r="G140" s="60" t="s">
+        <v>331</v>
+      </c>
+      <c r="H140" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="I140" s="71"/>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="65" t="s">
+        <v>324</v>
+      </c>
+      <c r="B141" s="59">
+        <v>35</v>
+      </c>
+      <c r="C141" s="61"/>
+      <c r="D141" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="E141" s="59">
+        <v>5</v>
+      </c>
+      <c r="F141" s="59">
+        <v>1</v>
+      </c>
+      <c r="G141" s="55"/>
+      <c r="H141" s="66" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="13.9" thickBot="1">
+      <c r="A142" s="67" t="s">
+        <v>325</v>
+      </c>
+      <c r="B142" s="68">
+        <v>20</v>
+      </c>
+      <c r="C142" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="D142" s="68" t="s">
+        <v>326</v>
+      </c>
+      <c r="E142" s="68">
+        <v>4</v>
+      </c>
+      <c r="F142" s="68">
+        <v>1</v>
+      </c>
+      <c r="G142" s="55"/>
+      <c r="H142" s="70" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E30F886-FCE8-4C02-BCB6-0CC031C0C7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCDFC2B-D88C-44B6-9203-D3DBC6873F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -1049,10 +1049,10 @@
     <t>暂时冻结受影响的敌人，并造成20点伤害；远程武器</t>
   </si>
   <si>
-    <t>让受影响的敌人中毒，18秒内造成120点伤害；远程武器：炼金卓制作，且概率失败变为蘑菇浸剂</t>
-  </si>
-  <si>
     <t>墓地蘑菇：20；艾莎眼泪：2</t>
+  </si>
+  <si>
+    <t>让受影响的敌人中毒，18秒内造成120点伤害；远程武器：炼金桌制作，且概率失败变为蘑菇浸剂</t>
   </si>
 </sst>
 </file>
@@ -5453,10 +5453,10 @@
         <v>1</v>
       </c>
       <c r="G140" s="60" t="s">
+        <v>330</v>
+      </c>
+      <c r="H140" s="72" t="s">
         <v>331</v>
-      </c>
-      <c r="H140" s="72" t="s">
-        <v>330</v>
       </c>
       <c r="I140" s="71"/>
     </row>
@@ -5515,12 +5515,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5743,17 +5742,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5778,18 +5787,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCDFC2B-D88C-44B6-9203-D3DBC6873F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8401C704-18F4-4862-BCC2-98C6E1B45EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -1229,12 +1229,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF351C75"/>
-        <bgColor rgb="FFFBBC04"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF4A86E8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1249,6 +1243,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFBBC04"/>
       </patternFill>
     </fill>
   </fills>
@@ -1814,7 +1814,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1829,9 +1829,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1875,7 +1872,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1908,7 +1905,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1926,16 +1923,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1961,6 +1958,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2315,16 +2315,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.4" thickBot="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="74"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="16" t="s">
@@ -2581,7 +2581,7 @@
         <v>33</v>
       </c>
       <c r="H12" s="23"/>
-      <c r="L12" s="46"/>
+      <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="24" t="s">
@@ -2647,7 +2647,7 @@
       <c r="G15" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="H15" s="47" t="s">
+      <c r="H15" s="46" t="s">
         <v>303</v>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       <c r="G24" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="H24" s="47" t="s">
+      <c r="H24" s="46" t="s">
         <v>302</v>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="14.65">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="75" t="s">
         <v>293</v>
       </c>
       <c r="B42" s="6">
@@ -3260,7 +3260,7 @@
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="31" t="s">
         <v>92</v>
       </c>
       <c r="B43" s="6">
@@ -3641,7 +3641,7 @@
         <v>100</v>
       </c>
       <c r="G59" s="2"/>
-      <c r="H59" s="33" t="s">
+      <c r="H59" s="32" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>67</v>
       </c>
       <c r="G60" s="2"/>
-      <c r="H60" s="33" t="s">
+      <c r="H60" s="32" t="s">
         <v>282</v>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
         <v>91</v>
       </c>
       <c r="G63" s="2"/>
-      <c r="H63" s="34" t="s">
+      <c r="H63" s="33" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.9" customHeight="1">
-      <c r="A64" s="35" t="s">
+      <c r="A64" s="34" t="s">
         <v>140</v>
       </c>
       <c r="B64" s="6">
@@ -3757,7 +3757,7 @@
       <c r="G64" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="H64" s="53" t="s">
+      <c r="H64" s="52" t="s">
         <v>316</v>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="27">
-      <c r="A69" s="36" t="s">
+      <c r="A69" s="35" t="s">
         <v>151</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -3931,7 +3931,7 @@
         <v>56</v>
       </c>
       <c r="G72" s="2"/>
-      <c r="H72" s="37" t="s">
+      <c r="H72" s="36" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
         <v>77</v>
       </c>
       <c r="G74" s="2"/>
-      <c r="H74" s="37" t="s">
+      <c r="H74" s="36" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
         <v>63</v>
       </c>
       <c r="G75" s="2"/>
-      <c r="H75" s="38" t="s">
+      <c r="H75" s="37" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       <c r="G80" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="H80" s="39"/>
+      <c r="H80" s="38"/>
     </row>
     <row r="81" spans="1:8" ht="28.9" customHeight="1">
       <c r="A81" s="27" t="s">
@@ -4137,7 +4137,7 @@
         <v>67</v>
       </c>
       <c r="G81" s="2"/>
-      <c r="H81" s="37" t="s">
+      <c r="H81" s="36" t="s">
         <v>177</v>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       <c r="G82" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="H82" s="38" t="s">
+      <c r="H82" s="37" t="s">
         <v>180</v>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       <c r="G83" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="H83" s="38" t="s">
+      <c r="H83" s="37" t="s">
         <v>312</v>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
         <v>67</v>
       </c>
       <c r="G85" s="2"/>
-      <c r="H85" s="37" t="s">
+      <c r="H85" s="36" t="s">
         <v>187</v>
       </c>
     </row>
@@ -4250,10 +4250,10 @@
       <c r="F86" s="6">
         <v>59</v>
       </c>
-      <c r="G86" s="52" t="s">
+      <c r="G86" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="H86" s="38" t="s">
+      <c r="H86" s="37" t="s">
         <v>316</v>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
         <v>84</v>
       </c>
       <c r="G87" s="2"/>
-      <c r="H87" s="38" t="s">
+      <c r="H87" s="37" t="s">
         <v>316</v>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       <c r="G88" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="H88" s="38" t="s">
+      <c r="H88" s="37" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
         <v>46</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="40" t="s">
+      <c r="H92" s="39" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
         <v>72</v>
       </c>
       <c r="G93" s="2"/>
-      <c r="H93" s="41" t="s">
+      <c r="H93" s="40" t="s">
         <v>202</v>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="38" t="s">
+      <c r="H95" s="37" t="s">
         <v>284</v>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
         <v>50</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="37" t="s">
+      <c r="H96" s="36" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="42" t="s">
+      <c r="A103" s="41" t="s">
         <v>220</v>
       </c>
       <c r="B103" s="6" t="s">
@@ -4647,7 +4647,7 @@
       <c r="G104" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="H104" s="54" t="s">
+      <c r="H104" s="53" t="s">
         <v>316</v>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="31.9" customHeight="1">
-      <c r="A110" s="43" t="s">
+      <c r="A110" s="42" t="s">
         <v>285</v>
       </c>
       <c r="B110" s="6">
@@ -4781,7 +4781,7 @@
         <v>46</v>
       </c>
       <c r="G110" s="2"/>
-      <c r="H110" s="44" t="s">
+      <c r="H110" s="43" t="s">
         <v>287</v>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
         <v>40</v>
       </c>
       <c r="G111" s="2"/>
-      <c r="H111" s="37" t="s">
+      <c r="H111" s="36" t="s">
         <v>231</v>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
         <v>100</v>
       </c>
       <c r="G112" s="2"/>
-      <c r="H112" s="37" t="s">
+      <c r="H112" s="36" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
         <v>50</v>
       </c>
       <c r="G113" s="2"/>
-      <c r="H113" s="37" t="s">
+      <c r="H113" s="36" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
         <v>72</v>
       </c>
       <c r="G114" s="2"/>
-      <c r="H114" s="37" t="s">
+      <c r="H114" s="36" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
         <v>100</v>
       </c>
       <c r="G115" s="2"/>
-      <c r="H115" s="44" t="s">
+      <c r="H115" s="43" t="s">
         <v>295</v>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
         <v>50</v>
       </c>
       <c r="G116" s="2"/>
-      <c r="H116" s="37" t="s">
+      <c r="H116" s="36" t="s">
         <v>235</v>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
         <v>72</v>
       </c>
       <c r="G119" s="2"/>
-      <c r="H119" s="33" t="s">
+      <c r="H119" s="32" t="s">
         <v>243</v>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
         <v>46</v>
       </c>
       <c r="G122" s="2"/>
-      <c r="H122" s="37" t="s">
+      <c r="H122" s="36" t="s">
         <v>250</v>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
         <v>50</v>
       </c>
       <c r="G123" s="2"/>
-      <c r="H123" s="37" t="s">
+      <c r="H123" s="36" t="s">
         <v>252</v>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
         <v>67</v>
       </c>
       <c r="G124" s="2"/>
-      <c r="H124" s="33" t="s">
+      <c r="H124" s="32" t="s">
         <v>254</v>
       </c>
     </row>
@@ -5139,7 +5139,7 @@
         <v>67</v>
       </c>
       <c r="G126" s="2"/>
-      <c r="H126" s="33" t="s">
+      <c r="H126" s="32" t="s">
         <v>258</v>
       </c>
     </row>
@@ -5161,7 +5161,7 @@
         <v>98</v>
       </c>
       <c r="G127" s="2"/>
-      <c r="H127" s="33" t="s">
+      <c r="H127" s="32" t="s">
         <v>258</v>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       <c r="G130" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="H130" s="37" t="s">
+      <c r="H130" s="36" t="s">
         <v>280</v>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
     </row>
     <row r="132" spans="1:9" ht="30" customHeight="1">
-      <c r="A132" s="45" t="s">
+      <c r="A132" s="44" t="s">
         <v>264</v>
       </c>
       <c r="B132" s="6" t="s">
@@ -5275,7 +5275,7 @@
         <v>53</v>
       </c>
       <c r="G132" s="2"/>
-      <c r="H132" s="38" t="s">
+      <c r="H132" s="37" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
         <v>46</v>
       </c>
       <c r="G133" s="2"/>
-      <c r="H133" s="38" t="s">
+      <c r="H133" s="37" t="s">
         <v>278</v>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
         <v>50</v>
       </c>
       <c r="G134" s="2"/>
-      <c r="H134" s="33" t="s">
+      <c r="H134" s="32" t="s">
         <v>268</v>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
         <v>50</v>
       </c>
       <c r="G135" s="2"/>
-      <c r="H135" s="37" t="s">
+      <c r="H135" s="36" t="s">
         <v>270</v>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
         <v>46</v>
       </c>
       <c r="G136" s="2"/>
-      <c r="H136" s="37" t="s">
+      <c r="H136" s="36" t="s">
         <v>272</v>
       </c>
     </row>
@@ -5385,124 +5385,124 @@
         <v>63</v>
       </c>
       <c r="G137" s="2"/>
-      <c r="H137" s="37" t="s">
+      <c r="H137" s="36" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="48" t="s">
+      <c r="A138" s="47" t="s">
         <v>274</v>
       </c>
-      <c r="B138" s="49" t="s">
+      <c r="B138" s="48" t="s">
         <v>275</v>
       </c>
-      <c r="C138" s="50"/>
-      <c r="D138" s="49">
+      <c r="C138" s="49"/>
+      <c r="D138" s="48">
         <v>0.8</v>
       </c>
-      <c r="E138" s="49">
+      <c r="E138" s="48">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F138" s="49">
+      <c r="F138" s="48">
         <v>50</v>
       </c>
-      <c r="G138" s="55"/>
-      <c r="H138" s="51" t="s">
+      <c r="G138" s="54"/>
+      <c r="H138" s="50" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:9">
-      <c r="A139" s="62" t="s">
+      <c r="A139" s="61" t="s">
         <v>306</v>
       </c>
-      <c r="B139" s="56" t="s">
+      <c r="B139" s="55" t="s">
         <v>307</v>
       </c>
-      <c r="C139" s="50"/>
-      <c r="D139" s="56">
+      <c r="C139" s="49"/>
+      <c r="D139" s="55">
         <v>1</v>
       </c>
-      <c r="E139" s="56">
+      <c r="E139" s="55">
         <v>2</v>
       </c>
-      <c r="F139" s="56">
+      <c r="F139" s="55">
         <v>143</v>
       </c>
-      <c r="G139" s="55"/>
-      <c r="H139" s="63" t="s">
+      <c r="G139" s="54"/>
+      <c r="H139" s="62" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="27">
-      <c r="A140" s="64" t="s">
+      <c r="A140" s="63" t="s">
         <v>323</v>
       </c>
-      <c r="B140" s="57" t="s">
+      <c r="B140" s="56" t="s">
         <v>326</v>
       </c>
-      <c r="C140" s="58" t="s">
+      <c r="C140" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="D140" s="57" t="s">
+      <c r="D140" s="56" t="s">
         <v>326</v>
       </c>
-      <c r="E140" s="57">
+      <c r="E140" s="56">
         <v>5</v>
       </c>
-      <c r="F140" s="57">
+      <c r="F140" s="56">
         <v>1</v>
       </c>
-      <c r="G140" s="60" t="s">
+      <c r="G140" s="59" t="s">
         <v>330</v>
       </c>
-      <c r="H140" s="72" t="s">
+      <c r="H140" s="71" t="s">
         <v>331</v>
       </c>
-      <c r="I140" s="71"/>
+      <c r="I140" s="70"/>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="65" t="s">
+      <c r="A141" s="64" t="s">
         <v>324</v>
       </c>
-      <c r="B141" s="59">
+      <c r="B141" s="58">
         <v>35</v>
       </c>
-      <c r="C141" s="61"/>
-      <c r="D141" s="59" t="s">
+      <c r="C141" s="60"/>
+      <c r="D141" s="58" t="s">
         <v>326</v>
       </c>
-      <c r="E141" s="59">
+      <c r="E141" s="58">
         <v>5</v>
       </c>
-      <c r="F141" s="59">
+      <c r="F141" s="58">
         <v>1</v>
       </c>
-      <c r="G141" s="55"/>
-      <c r="H141" s="66" t="s">
+      <c r="G141" s="54"/>
+      <c r="H141" s="65" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="13.9" thickBot="1">
-      <c r="A142" s="67" t="s">
+      <c r="A142" s="66" t="s">
         <v>325</v>
       </c>
-      <c r="B142" s="68">
+      <c r="B142" s="67">
         <v>20</v>
       </c>
-      <c r="C142" s="69" t="s">
+      <c r="C142" s="68" t="s">
         <v>165</v>
       </c>
-      <c r="D142" s="68" t="s">
+      <c r="D142" s="67" t="s">
         <v>326</v>
       </c>
-      <c r="E142" s="68">
+      <c r="E142" s="67">
         <v>4</v>
       </c>
-      <c r="F142" s="68">
+      <c r="F142" s="67">
         <v>1</v>
       </c>
-      <c r="G142" s="55"/>
-      <c r="H142" s="70" t="s">
+      <c r="G142" s="54"/>
+      <c r="H142" s="69" t="s">
         <v>329</v>
       </c>
     </row>
@@ -5523,6 +5523,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -5741,15 +5750,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
   <ds:schemaRefs>
@@ -5768,6 +5768,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5784,12 +5792,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8401C704-18F4-4862-BCC2-98C6E1B45EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06133C3A-1424-4483-83E1-0D99360A1CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -980,12 +980,6 @@
     <t>黑色弗兰贝尔格</t>
   </si>
   <si>
-    <t>162+15</t>
-  </si>
-  <si>
-    <t>使用这种武器攻击会使目标的治疗降为0.持续10秒</t>
-  </si>
-  <si>
     <t>百病之斧</t>
   </si>
   <si>
@@ -1043,16 +1037,22 @@
     <t>120 毒伤</t>
   </si>
   <si>
-    <t>对受影响的敌人造成恐惧，并造成35点伤害；远程武器</t>
-  </si>
-  <si>
-    <t>暂时冻结受影响的敌人，并造成20点伤害；远程武器</t>
-  </si>
-  <si>
     <t>墓地蘑菇：20；艾莎眼泪：2</t>
   </si>
   <si>
-    <t>让受影响的敌人中毒，18秒内造成120点伤害；远程武器：炼金桌制作，且概率失败变为蘑菇浸剂</t>
+    <t>150+15</t>
+  </si>
+  <si>
+    <t>使用这种武器攻击会使目标的治疗降为0，持续10秒；被动伤敌护甲</t>
+  </si>
+  <si>
+    <t>让受影响的敌人中毒，18秒内造成120点伤害；远程武器；炼金桌制作，且概率失败变为蘑菇浸剂</t>
+  </si>
+  <si>
+    <t>对受影响的敌人造成恐惧，并造成35点伤害；远程武器；</t>
+  </si>
+  <si>
+    <t>暂时冻结受影响的敌人，并造成20点伤害；远程武器；</t>
   </si>
 </sst>
 </file>
@@ -1920,9 +1920,6 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1950,6 +1947,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1958,9 +1961,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2315,16 +2315,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.4" thickBot="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="74"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="16" t="s">
@@ -2390,7 +2390,7 @@
         <v>13</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>14</v>
@@ -2645,7 +2645,7 @@
         <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H15" s="46" t="s">
         <v>303</v>
@@ -2781,7 +2781,7 @@
         <v>84</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H21" s="21"/>
     </row>
@@ -2845,7 +2845,7 @@
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H24" s="46" t="s">
         <v>302</v>
@@ -2869,7 +2869,7 @@
         <v>84</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H25" s="23" t="s">
         <v>59</v>
@@ -3050,7 +3050,7 @@
         <v>75</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="13.9">
@@ -3232,11 +3232,11 @@
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="23" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="14.65">
-      <c r="A42" s="75" t="s">
+      <c r="A42" s="71" t="s">
         <v>293</v>
       </c>
       <c r="B42" s="6">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="23" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="23" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="13.9">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="13.9">
@@ -3620,7 +3620,7 @@
         <v>129</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -3758,7 +3758,7 @@
         <v>141</v>
       </c>
       <c r="H64" s="52" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="27" customHeight="1">
@@ -4027,7 +4027,7 @@
     </row>
     <row r="77" spans="1:8" ht="14.25">
       <c r="A77" s="27" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>160</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -4186,7 +4186,7 @@
         <v>153</v>
       </c>
       <c r="H83" s="37" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="26.25" customHeight="1">
@@ -4251,10 +4251,10 @@
         <v>59</v>
       </c>
       <c r="G86" s="51" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="37" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="27">
@@ -4648,7 +4648,7 @@
         <v>223</v>
       </c>
       <c r="H104" s="53" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="23" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="23" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="23" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="23" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="45.75" customHeight="1">
@@ -5411,12 +5411,12 @@
         <v>276</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" ht="27">
       <c r="A139" s="61" t="s">
         <v>306</v>
       </c>
       <c r="B139" s="55" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="C139" s="49"/>
       <c r="D139" s="55">
@@ -5429,22 +5429,22 @@
         <v>143</v>
       </c>
       <c r="G139" s="54"/>
-      <c r="H139" s="62" t="s">
-        <v>308</v>
+      <c r="H139" s="72" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="27">
-      <c r="A140" s="63" t="s">
-        <v>323</v>
+      <c r="A140" s="62" t="s">
+        <v>321</v>
       </c>
       <c r="B140" s="56" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C140" s="57" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D140" s="56" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E140" s="56">
         <v>5</v>
@@ -5453,23 +5453,23 @@
         <v>1</v>
       </c>
       <c r="G140" s="59" t="s">
-        <v>330</v>
-      </c>
-      <c r="H140" s="71" t="s">
-        <v>331</v>
-      </c>
-      <c r="I140" s="70"/>
+        <v>326</v>
+      </c>
+      <c r="H140" s="70" t="s">
+        <v>329</v>
+      </c>
+      <c r="I140" s="69"/>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="64" t="s">
-        <v>324</v>
+      <c r="A141" s="63" t="s">
+        <v>322</v>
       </c>
       <c r="B141" s="58">
         <v>35</v>
       </c>
       <c r="C141" s="60"/>
       <c r="D141" s="58" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E141" s="58">
         <v>5</v>
@@ -5478,32 +5478,32 @@
         <v>1</v>
       </c>
       <c r="G141" s="54"/>
-      <c r="H141" s="65" t="s">
-        <v>328</v>
+      <c r="H141" s="64" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="13.9" thickBot="1">
-      <c r="A142" s="66" t="s">
-        <v>325</v>
-      </c>
-      <c r="B142" s="67">
+      <c r="A142" s="65" t="s">
+        <v>323</v>
+      </c>
+      <c r="B142" s="66">
         <v>20</v>
       </c>
-      <c r="C142" s="68" t="s">
+      <c r="C142" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="D142" s="67" t="s">
-        <v>326</v>
-      </c>
-      <c r="E142" s="67">
+      <c r="D142" s="66" t="s">
+        <v>324</v>
+      </c>
+      <c r="E142" s="66">
         <v>4</v>
       </c>
-      <c r="F142" s="67">
+      <c r="F142" s="66">
         <v>1</v>
       </c>
       <c r="G142" s="54"/>
-      <c r="H142" s="69" t="s">
-        <v>329</v>
+      <c r="H142" s="68" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06133C3A-1424-4483-83E1-0D99360A1CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BE628D-6412-4D1F-81DE-EB9F41AED9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -737,9 +737,6 @@
     <t>95+15</t>
   </si>
   <si>
-    <t>对人的伤害增加至1.5倍</t>
-  </si>
-  <si>
     <t>战犬之斧</t>
   </si>
   <si>
@@ -788,9 +785,6 @@
     <t>银制双刃大砍刀</t>
   </si>
   <si>
-    <t>对怪物的伤害增加至1.5倍</t>
-  </si>
-  <si>
     <t>诸神之怒</t>
   </si>
   <si>
@@ -1007,9 +1001,6 @@
     <t>几率点燃敌人（5火伤*5下）；吓退夜游神；远程武器</t>
   </si>
   <si>
-    <t>狼和恐狼对受影响的目标造成更多伤害；远程武器</t>
-  </si>
-  <si>
     <t>减慢对手的攻击与奔跑速度；远程武器</t>
   </si>
   <si>
@@ -1053,6 +1044,15 @@
   </si>
   <si>
     <t>暂时冻结受影响的敌人，并造成20点伤害；远程武器；</t>
+  </si>
+  <si>
+    <t>对人的伤害增加至1.4倍</t>
+  </si>
+  <si>
+    <t>对怪物的伤害增加至1.4倍</t>
+  </si>
+  <si>
+    <t>狼（被控制的野生狼）和恐狼（宠物）对受影响的目标造成更多伤害（2秒/30衰败伤）；远程武器</t>
   </si>
 </sst>
 </file>
@@ -2311,12 +2311,12 @@
     <col min="2" max="2" width="16.46484375" customWidth="1"/>
     <col min="3" max="3" width="10.59765625" customWidth="1"/>
     <col min="7" max="7" width="30.86328125" customWidth="1"/>
-    <col min="8" max="8" width="47.9296875" customWidth="1"/>
+    <col min="8" max="8" width="49.9296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.4" thickBot="1">
       <c r="A1" s="73" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B1" s="74"/>
       <c r="C1" s="74"/>
@@ -2390,7 +2390,7 @@
         <v>13</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>14</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="15" spans="1:12" ht="13.9">
       <c r="A15" s="26" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B15" s="1">
         <v>18</v>
@@ -2645,10 +2645,10 @@
         <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="13.9">
@@ -2781,7 +2781,7 @@
         <v>84</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H21" s="21"/>
     </row>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="24" spans="1:8" ht="13.9">
       <c r="A24" s="26" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B24" s="1">
         <v>20</v>
@@ -2845,10 +2845,10 @@
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="13.9">
@@ -2869,7 +2869,7 @@
         <v>84</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H25" s="23" t="s">
         <v>59</v>
@@ -3050,7 +3050,7 @@
         <v>75</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="13.9">
@@ -3232,18 +3232,18 @@
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="23" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="14.65">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="28.15">
       <c r="A42" s="71" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B42" s="6">
         <v>30</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D42" s="6">
         <v>0.8</v>
@@ -3255,8 +3255,8 @@
         <v>46</v>
       </c>
       <c r="G42" s="2"/>
-      <c r="H42" s="23" t="s">
-        <v>316</v>
+      <c r="H42" s="33" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="23" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="13.9">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="13.9">
@@ -3620,7 +3620,7 @@
         <v>129</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -3664,18 +3664,18 @@
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="32" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="14.65">
       <c r="A61" s="28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D61" s="6">
         <v>1.5</v>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="23" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="14.65">
@@ -3758,7 +3758,7 @@
         <v>141</v>
       </c>
       <c r="H64" s="52" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="27" customHeight="1">
@@ -4027,13 +4027,13 @@
     </row>
     <row r="77" spans="1:8" ht="14.25">
       <c r="A77" s="27" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D77" s="6">
         <v>0.9</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="23" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -4186,7 +4186,7 @@
         <v>153</v>
       </c>
       <c r="H83" s="37" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="26.25" customHeight="1">
@@ -4251,10 +4251,10 @@
         <v>59</v>
       </c>
       <c r="G86" s="51" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="37" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="27">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="37" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="30.75" customHeight="1">
@@ -4648,7 +4648,7 @@
         <v>223</v>
       </c>
       <c r="H104" s="53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -4675,7 +4675,7 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="28" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B106" s="6">
         <v>90</v>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="23" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="28" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B107" s="6">
         <v>90</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="23" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="23" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -4758,18 +4758,18 @@
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="23" t="s">
-        <v>229</v>
+        <v>329</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="31.9" customHeight="1">
       <c r="A110" s="42" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B110" s="6">
         <v>95</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D110" s="6">
         <v>1</v>
@@ -4782,12 +4782,12 @@
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="43" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="30.75" customHeight="1">
       <c r="A111" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B111" s="6">
         <v>95</v>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="31.15" customHeight="1">
       <c r="A112" s="28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B112" s="6">
         <v>98</v>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="36" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="31.15" customHeight="1">
       <c r="A113" s="28" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B113" s="6">
         <v>100</v>
@@ -4848,12 +4848,12 @@
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="36" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="31.15" customHeight="1">
       <c r="A114" s="28" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B114" s="6">
         <v>100</v>
@@ -4870,12 +4870,12 @@
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="36" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="31.15" customHeight="1">
       <c r="A115" s="28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B115" s="6">
         <v>100</v>
@@ -4892,12 +4892,12 @@
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="33" customHeight="1">
       <c r="A116" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B116" s="6">
         <v>100</v>
@@ -4914,18 +4914,18 @@
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="14.65">
       <c r="A117" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="B117" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B117" s="6" t="s">
+      <c r="C117" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="D117" s="6">
         <v>0.8</v>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B118" s="6">
         <v>100</v>
@@ -4960,15 +4960,15 @@
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="6">
@@ -4982,15 +4982,15 @@
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C120" s="10"/>
       <c r="D120" s="6">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="23" t="s">
-        <v>245</v>
+        <v>330</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B121" s="6">
         <v>100</v>
@@ -5026,18 +5026,18 @@
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="18.399999999999999" customHeight="1">
       <c r="A122" s="28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B122" s="6">
         <v>105</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D122" s="6">
         <v>0.8</v>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="36" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="31.15" customHeight="1">
       <c r="A123" s="28" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B123" s="6">
         <v>105</v>
@@ -5074,12 +5074,12 @@
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="27" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B124" s="6">
         <v>107</v>
@@ -5096,12 +5096,12 @@
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="32" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="28" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B125" s="6">
         <v>110</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="23" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="28" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B126" s="6">
         <v>110</v>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="32" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="28" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B127" s="6">
         <v>110</v>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="32" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="28" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B128" s="6">
         <v>112</v>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="28" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B129" s="6">
         <v>120</v>
@@ -5206,15 +5206,15 @@
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="23" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="45.75" customHeight="1">
       <c r="A130" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="B130" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="C130" s="10"/>
       <c r="D130" s="6">
@@ -5227,15 +5227,15 @@
         <v>50</v>
       </c>
       <c r="G130" s="13" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H130" s="36" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="28" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B131" s="6">
         <v>128</v>
@@ -5252,15 +5252,15 @@
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="23" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="30" customHeight="1">
       <c r="A132" s="44" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>214</v>
@@ -5276,15 +5276,15 @@
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="37" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="17.649999999999999" customHeight="1">
       <c r="A133" s="28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="6">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="37" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="28" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B134" s="6">
         <v>130</v>
@@ -5320,12 +5320,12 @@
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="31.5" customHeight="1">
       <c r="A135" s="28" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B135" s="6">
         <v>132</v>
@@ -5342,12 +5342,12 @@
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="36" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="34.5" customHeight="1">
       <c r="A136" s="28" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B136" s="6">
         <v>132</v>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="36" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="33" customHeight="1">
       <c r="A137" s="28" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B137" s="6">
         <v>132</v>
@@ -5386,15 +5386,15 @@
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="36" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="47" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B138" s="48" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C138" s="49"/>
       <c r="D138" s="48">
@@ -5408,15 +5408,15 @@
       </c>
       <c r="G138" s="54"/>
       <c r="H138" s="50" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="27">
       <c r="A139" s="61" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B139" s="55" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C139" s="49"/>
       <c r="D139" s="55">
@@ -5430,21 +5430,21 @@
       </c>
       <c r="G139" s="54"/>
       <c r="H139" s="72" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="27">
       <c r="A140" s="62" t="s">
+        <v>318</v>
+      </c>
+      <c r="B140" s="56" t="s">
         <v>321</v>
       </c>
-      <c r="B140" s="56" t="s">
-        <v>324</v>
-      </c>
       <c r="C140" s="57" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D140" s="56" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E140" s="56">
         <v>5</v>
@@ -5453,23 +5453,23 @@
         <v>1</v>
       </c>
       <c r="G140" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="H140" s="70" t="s">
         <v>326</v>
-      </c>
-      <c r="H140" s="70" t="s">
-        <v>329</v>
       </c>
       <c r="I140" s="69"/>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="63" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B141" s="58">
         <v>35</v>
       </c>
       <c r="C141" s="60"/>
       <c r="D141" s="58" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E141" s="58">
         <v>5</v>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="G141" s="54"/>
       <c r="H141" s="64" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="13.9" thickBot="1">
       <c r="A142" s="65" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B142" s="66">
         <v>20</v>
@@ -5493,7 +5493,7 @@
         <v>165</v>
       </c>
       <c r="D142" s="66" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E142" s="66">
         <v>4</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="G142" s="54"/>
       <c r="H142" s="68" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -5515,20 +5515,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5751,6 +5751,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -5763,14 +5771,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BE628D-6412-4D1F-81DE-EB9F41AED9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4381DF-3336-4CDD-8183-E822A89A8D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -1037,9 +1037,6 @@
     <t>使用这种武器攻击会使目标的治疗降为0，持续10秒；被动伤敌护甲</t>
   </si>
   <si>
-    <t>让受影响的敌人中毒，18秒内造成120点伤害；远程武器；炼金桌制作，且概率失败变为蘑菇浸剂</t>
-  </si>
-  <si>
     <t>对受影响的敌人造成恐惧，并造成35点伤害；远程武器；</t>
   </si>
   <si>
@@ -1053,6 +1050,9 @@
   </si>
   <si>
     <t>狼（被控制的野生狼）和恐狼（宠物）对受影响的目标造成更多伤害（2秒/30衰败伤）；远程武器</t>
+  </si>
+  <si>
+    <t>让受影响的敌人中毒，18秒内造成120点伤害；炼金桌制作，且概率失败变为蘑菇浸剂；远程武器；</t>
   </si>
 </sst>
 </file>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="33" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -4387,7 +4387,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27">
+    <row r="93" spans="1:8">
       <c r="A93" s="28" t="s">
         <v>200</v>
       </c>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="31.9" customHeight="1">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -5456,7 +5456,7 @@
         <v>323</v>
       </c>
       <c r="H140" s="70" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="I140" s="69"/>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="G141" s="54"/>
       <c r="H141" s="64" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="13.9" thickBot="1">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="G142" s="54"/>
       <c r="H142" s="68" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -5515,20 +5515,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5751,14 +5751,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -5771,6 +5763,14 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/武器数据.xlsx
+++ b/data-source/武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4381DF-3336-4CDD-8183-E822A89A8D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6E327A-1ACC-4EF9-B829-B9C48772433A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -5187,130 +5187,130 @@
         <v>259</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
-      <c r="A129" s="28" t="s">
-        <v>294</v>
-      </c>
-      <c r="B129" s="6">
-        <v>120</v>
+    <row r="129" spans="1:9" ht="40.5">
+      <c r="A129" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>279</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="6">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E129" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6">
-        <v>100</v>
-      </c>
-      <c r="G129" s="2"/>
-      <c r="H129" s="23" t="s">
-        <v>317</v>
+        <v>50</v>
+      </c>
+      <c r="G129" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="H129" s="36" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="45.75" customHeight="1">
-      <c r="A130" s="27" t="s">
-        <v>277</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>279</v>
+      <c r="A130" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="B130" s="6">
+        <v>128</v>
       </c>
       <c r="C130" s="10"/>
       <c r="D130" s="6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E130" s="6">
         <v>2</v>
       </c>
       <c r="F130" s="6">
-        <v>50</v>
-      </c>
-      <c r="G130" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="H130" s="36" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9">
-      <c r="A131" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="B131" s="6">
-        <v>128</v>
-      </c>
-      <c r="C131" s="10"/>
+        <v>46</v>
+      </c>
+      <c r="G130" s="2"/>
+      <c r="H130" s="23" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="28.5">
+      <c r="A131" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>214</v>
+      </c>
       <c r="D131" s="6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E131" s="6">
         <v>2</v>
       </c>
       <c r="F131" s="6">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G131" s="2"/>
-      <c r="H131" s="23" t="s">
-        <v>261</v>
+      <c r="H131" s="37" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="30" customHeight="1">
-      <c r="A132" s="44" t="s">
-        <v>262</v>
+      <c r="A132" s="28" t="s">
+        <v>275</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C132" s="8" t="s">
-        <v>214</v>
-      </c>
+      <c r="C132" s="10"/>
       <c r="D132" s="6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E132" s="6">
         <v>2</v>
       </c>
       <c r="F132" s="6">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="37" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="17.649999999999999" customHeight="1">
       <c r="A133" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="B133" s="6">
+        <v>130</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E133" s="6">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F133" s="6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G133" s="2"/>
-      <c r="H133" s="37" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9">
+      <c r="H133" s="32" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="27">
       <c r="A134" s="28" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B134" s="6">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C134" s="10"/>
       <c r="D134" s="6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E134" s="6">
         <v>2.2999999999999998</v>
@@ -5319,13 +5319,13 @@
         <v>50</v>
       </c>
       <c r="G134" s="2"/>
-      <c r="H134" s="32" t="s">
-        <v>266</v>
+      <c r="H134" s="36" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="31.5" customHeight="1">
       <c r="A135" s="28" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B135" s="6">
         <v>132</v>
@@ -5338,16 +5338,16 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F135" s="6">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="36" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="34.5" customHeight="1">
       <c r="A136" s="28" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B136" s="6">
         <v>132</v>
@@ -5360,7 +5360,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F136" s="6">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="36" t="s">
@@ -5368,47 +5368,47 @@
       </c>
     </row>
     <row r="137" spans="1:9" ht="33" customHeight="1">
-      <c r="A137" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="B137" s="6">
-        <v>132</v>
-      </c>
-      <c r="C137" s="10"/>
-      <c r="D137" s="6">
+      <c r="A137" s="47" t="s">
+        <v>272</v>
+      </c>
+      <c r="B137" s="48" t="s">
+        <v>273</v>
+      </c>
+      <c r="C137" s="49"/>
+      <c r="D137" s="48">
         <v>0.8</v>
       </c>
-      <c r="E137" s="6">
+      <c r="E137" s="48">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F137" s="6">
-        <v>63</v>
-      </c>
-      <c r="G137" s="2"/>
-      <c r="H137" s="36" t="s">
-        <v>270</v>
+      <c r="F137" s="48">
+        <v>50</v>
+      </c>
+      <c r="G137" s="54"/>
+      <c r="H137" s="50" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="47" t="s">
-        <v>272</v>
-      </c>
-      <c r="B138" s="48" t="s">
-        <v>273</v>
-      </c>
-      <c r="C138" s="49"/>
-      <c r="D138" s="48">
-        <v>0.8</v>
-      </c>
-      <c r="E138" s="48">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F138" s="48">
-        <v>50</v>
-      </c>
-      <c r="G138" s="54"/>
-      <c r="H138" s="50" t="s">
-        <v>274</v>
+      <c r="A138" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="B138" s="6">
+        <v>150</v>
+      </c>
+      <c r="C138" s="10"/>
+      <c r="D138" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="E138" s="6">
+        <v>7</v>
+      </c>
+      <c r="F138" s="6">
+        <v>100</v>
+      </c>
+      <c r="G138" s="2"/>
+      <c r="H138" s="23" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="27">
@@ -5458,7 +5458,6 @@
       <c r="H140" s="70" t="s">
         <v>331</v>
       </c>
-      <c r="I140" s="69"/>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="63" t="s">
@@ -5481,6 +5480,7 @@
       <c r="H141" s="64" t="s">
         <v>326</v>
       </c>
+      <c r="I141" s="69"/>
     </row>
     <row r="142" spans="1:9" ht="13.9" thickBot="1">
       <c r="A142" s="65" t="s">
@@ -5515,20 +5515,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5751,6 +5751,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFFC337-698C-400C-A4B2-7E8A750F65D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -5763,14 +5771,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
